--- a/outputs/ESPAC LCIA.xlsx
+++ b/outputs/ESPAC LCIA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://irtacat-my.sharepoint.com/personal/angel_avadi_irta_cat/Documents/Documents/_Proyectos/ESPAC/outputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="96" documentId="11_F25DC773A252ABDACC104896819841BA5BDE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A3AED63-27DF-40A3-B95E-381B0332D51D}"/>
+  <xr:revisionPtr revIDLastSave="98" documentId="11_F25DC773A252ABDACC104896819841BA5BDE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E642F178-63FD-4DED-8365-9A0FC4E479E4}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-75" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ESPAC" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1396" uniqueCount="958">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1396" uniqueCount="955">
   <si>
     <t xml:space="preserve">Calculation: </t>
   </si>
@@ -1236,681 +1236,159 @@
     <t>crop: MANGO (FRUTA FRESCA) | category: permanent | summary: strategy_3</t>
   </si>
   <si>
-    <t>0,28559114</t>
-  </si>
-  <si>
     <t>-0,24896745</t>
   </si>
   <si>
     <t>0,79190578</t>
   </si>
   <si>
-    <t>0,20022057</t>
-  </si>
-  <si>
-    <t>0,37994556</t>
-  </si>
-  <si>
     <t>2,3876725</t>
   </si>
   <si>
     <t>0,15107911</t>
   </si>
   <si>
-    <t>0,34190211</t>
-  </si>
-  <si>
-    <t>0,061390845</t>
-  </si>
-  <si>
-    <t>-0,5789929</t>
-  </si>
-  <si>
-    <t>0,7765564</t>
-  </si>
-  <si>
     <t>0,5504073</t>
   </si>
   <si>
-    <t>6,388626</t>
-  </si>
-  <si>
-    <t>1,9071281</t>
-  </si>
-  <si>
-    <t>1,0554352</t>
-  </si>
-  <si>
-    <t>1,482158</t>
-  </si>
-  <si>
-    <t>0,15775023</t>
-  </si>
-  <si>
     <t>0,10211459</t>
   </si>
   <si>
-    <t>0,078536553</t>
-  </si>
-  <si>
-    <t>0,1021091</t>
-  </si>
-  <si>
-    <t>0,15962307</t>
-  </si>
-  <si>
-    <t>7,1042109</t>
-  </si>
-  <si>
     <t>1,7368229</t>
   </si>
   <si>
-    <t>17,577283</t>
-  </si>
-  <si>
     <t>0,86320837</t>
   </si>
   <si>
-    <t>0,097798813</t>
-  </si>
-  <si>
-    <t>0,52577438</t>
-  </si>
-  <si>
     <t>0,035299634</t>
   </si>
   <si>
     <t>0,18591769</t>
   </si>
   <si>
-    <t>1,953325</t>
-  </si>
-  <si>
-    <t>2,034914</t>
-  </si>
-  <si>
-    <t>1,2891536</t>
-  </si>
-  <si>
-    <t>0,39892361</t>
-  </si>
-  <si>
-    <t>0,22222717</t>
-  </si>
-  <si>
     <t>0,39163345</t>
   </si>
   <si>
-    <t>0,18051223</t>
-  </si>
-  <si>
     <t>0,18940804</t>
   </si>
   <si>
-    <t>-11,141083</t>
-  </si>
-  <si>
-    <t>0,13646157</t>
-  </si>
-  <si>
-    <t>0,24213989</t>
-  </si>
-  <si>
-    <t>0,12555802</t>
-  </si>
-  <si>
     <t>0,57817774</t>
   </si>
   <si>
-    <t>0,7759744</t>
-  </si>
-  <si>
-    <t>-4,7209797</t>
-  </si>
-  <si>
-    <t>1,2627085</t>
-  </si>
-  <si>
     <t>-0,0074745244</t>
   </si>
   <si>
-    <t>6,0357648</t>
-  </si>
-  <si>
-    <t>0,90394834</t>
-  </si>
-  <si>
-    <t>1,1977111</t>
-  </si>
-  <si>
-    <t>1,8980346</t>
-  </si>
-  <si>
-    <t>0,14120968</t>
-  </si>
-  <si>
-    <t>0,1505595</t>
-  </si>
-  <si>
-    <t>0,58289895</t>
-  </si>
-  <si>
-    <t>3,3124865</t>
-  </si>
-  <si>
-    <t>0,77492529</t>
-  </si>
-  <si>
-    <t>0,17680049</t>
-  </si>
-  <si>
-    <t>9,0429919</t>
-  </si>
-  <si>
     <t>0,21611207</t>
   </si>
   <si>
-    <t>1,3179017</t>
-  </si>
-  <si>
-    <t>-0,79283334</t>
-  </si>
-  <si>
-    <t>0,70346048</t>
-  </si>
-  <si>
-    <t>2,3385065</t>
-  </si>
-  <si>
-    <t>0,19524902</t>
-  </si>
-  <si>
     <t>5,3102423</t>
   </si>
   <si>
-    <t>-4,7039667</t>
-  </si>
-  <si>
-    <t>1,1309836</t>
-  </si>
-  <si>
-    <t>1,9141625</t>
-  </si>
-  <si>
-    <t>0,86695917</t>
-  </si>
-  <si>
-    <t>0,88829985</t>
-  </si>
-  <si>
-    <t>0,56056491</t>
-  </si>
-  <si>
-    <t>3,1749535</t>
-  </si>
-  <si>
-    <t>4,3049445</t>
-  </si>
-  <si>
-    <t>0,26900836</t>
-  </si>
-  <si>
     <t>0,54774474</t>
   </si>
   <si>
-    <t>0,47716243</t>
-  </si>
-  <si>
-    <t>0,031745401</t>
-  </si>
-  <si>
     <t>-0,24877077</t>
   </si>
   <si>
     <t>-0,0021082425</t>
   </si>
   <si>
-    <t>0,21111875</t>
-  </si>
-  <si>
-    <t>0,22533</t>
-  </si>
-  <si>
     <t>0,4048132</t>
   </si>
   <si>
     <t>0,078205386</t>
   </si>
   <si>
-    <t>0,18398097</t>
-  </si>
-  <si>
-    <t>0,015984009</t>
-  </si>
-  <si>
-    <t>-0,29203093</t>
-  </si>
-  <si>
-    <t>0,43184924</t>
-  </si>
-  <si>
     <t>0,11274495</t>
   </si>
   <si>
-    <t>3,5359601</t>
-  </si>
-  <si>
-    <t>0,88767111</t>
-  </si>
-  <si>
-    <t>0,15617694</t>
-  </si>
-  <si>
-    <t>0,86040495</t>
-  </si>
-  <si>
-    <t>0,08812918</t>
-  </si>
-  <si>
     <t>0,0048229873</t>
   </si>
   <si>
-    <t>0,066826874</t>
-  </si>
-  <si>
-    <t>0,060098887</t>
-  </si>
-  <si>
-    <t>0,075262835</t>
-  </si>
-  <si>
-    <t>4,771835</t>
-  </si>
-  <si>
     <t>0,058639549</t>
   </si>
   <si>
-    <t>11,796531</t>
-  </si>
-  <si>
     <t>0,51164379</t>
   </si>
   <si>
-    <t>0,076477903</t>
-  </si>
-  <si>
-    <t>0,40179899</t>
-  </si>
-  <si>
     <t>0,01033274</t>
   </si>
   <si>
     <t>0,048317946</t>
   </si>
   <si>
-    <t>1,0677914</t>
-  </si>
-  <si>
-    <t>1,0515709</t>
-  </si>
-  <si>
-    <t>0,60043914</t>
-  </si>
-  <si>
-    <t>0,16606728</t>
-  </si>
-  <si>
-    <t>0,10586757</t>
-  </si>
-  <si>
     <t>0,044445891</t>
   </si>
   <si>
-    <t>0,074194318</t>
-  </si>
-  <si>
     <t>0,036973312</t>
   </si>
   <si>
-    <t>-6,1633057</t>
-  </si>
-  <si>
-    <t>0,21579081</t>
-  </si>
-  <si>
-    <t>0,10582584</t>
-  </si>
-  <si>
-    <t>0,053022281</t>
-  </si>
-  <si>
     <t>0,33618769</t>
   </si>
   <si>
-    <t>0,15389805</t>
-  </si>
-  <si>
-    <t>-2,5775792</t>
-  </si>
-  <si>
-    <t>0,73367989</t>
-  </si>
-  <si>
     <t>-0,033021223</t>
   </si>
   <si>
-    <t>2,9148356</t>
-  </si>
-  <si>
-    <t>0,40060489</t>
-  </si>
-  <si>
-    <t>0,5893046</t>
-  </si>
-  <si>
-    <t>0,80900338</t>
-  </si>
-  <si>
-    <t>0,083099126</t>
-  </si>
-  <si>
-    <t>0,090060589</t>
-  </si>
-  <si>
-    <t>0,36658572</t>
-  </si>
-  <si>
-    <t>2,5036053</t>
-  </si>
-  <si>
-    <t>0,44290168</t>
-  </si>
-  <si>
-    <t>0,043791226</t>
-  </si>
-  <si>
-    <t>5,078183</t>
-  </si>
-  <si>
     <t>0,071990895</t>
   </si>
   <si>
-    <t>0,6818295</t>
-  </si>
-  <si>
-    <t>-0,50374753</t>
-  </si>
-  <si>
-    <t>0,0025858599</t>
-  </si>
-  <si>
-    <t>0,37089591</t>
-  </si>
-  <si>
-    <t>0,081796929</t>
-  </si>
-  <si>
     <t>-0,0028080186</t>
   </si>
   <si>
-    <t>-2,632819</t>
-  </si>
-  <si>
-    <t>0,75688071</t>
-  </si>
-  <si>
-    <t>1,0725913</t>
-  </si>
-  <si>
-    <t>0,50637907</t>
-  </si>
-  <si>
-    <t>0,014449031</t>
-  </si>
-  <si>
-    <t>0,32708874</t>
-  </si>
-  <si>
-    <t>1,8326772</t>
-  </si>
-  <si>
-    <t>2,5638528</t>
-  </si>
-  <si>
-    <t>0,19263461</t>
-  </si>
-  <si>
     <t>0,36591204</t>
   </si>
   <si>
-    <t>0,29830805</t>
-  </si>
-  <si>
-    <t>0,25384574</t>
-  </si>
-  <si>
     <t>-0,00019667923</t>
   </si>
   <si>
     <t>0,79401403</t>
   </si>
   <si>
-    <t>-0,010898179</t>
-  </si>
-  <si>
-    <t>0,15461556</t>
-  </si>
-  <si>
     <t>1,9828593</t>
   </si>
   <si>
     <t>0,072873721</t>
   </si>
   <si>
-    <t>0,15792114</t>
-  </si>
-  <si>
-    <t>0,045406836</t>
-  </si>
-  <si>
-    <t>-0,28696197</t>
-  </si>
-  <si>
-    <t>0,34470716</t>
-  </si>
-  <si>
     <t>0,43766234</t>
   </si>
   <si>
-    <t>2,8526658</t>
-  </si>
-  <si>
-    <t>1,0194569</t>
-  </si>
-  <si>
-    <t>0,89925821</t>
-  </si>
-  <si>
-    <t>0,62175304</t>
-  </si>
-  <si>
-    <t>0,069621047</t>
-  </si>
-  <si>
     <t>0,0972916</t>
   </si>
   <si>
-    <t>0,011709679</t>
-  </si>
-  <si>
-    <t>0,042010216</t>
-  </si>
-  <si>
-    <t>0,084360239</t>
-  </si>
-  <si>
-    <t>2,3323759</t>
-  </si>
-  <si>
     <t>1,6781833</t>
   </si>
   <si>
-    <t>5,7807522</t>
-  </si>
-  <si>
     <t>0,35156459</t>
   </si>
   <si>
-    <t>0,02132091</t>
-  </si>
-  <si>
-    <t>0,12397539</t>
-  </si>
-  <si>
     <t>0,024966893</t>
   </si>
   <si>
     <t>0,13759975</t>
   </si>
   <si>
-    <t>0,88553363</t>
-  </si>
-  <si>
-    <t>0,98334307</t>
-  </si>
-  <si>
-    <t>0,68871449</t>
-  </si>
-  <si>
-    <t>0,23285633</t>
-  </si>
-  <si>
-    <t>0,1163596</t>
-  </si>
-  <si>
     <t>0,34718756</t>
   </si>
   <si>
-    <t>0,10631792</t>
-  </si>
-  <si>
     <t>0,15243473</t>
   </si>
   <si>
-    <t>-4,9777772</t>
-  </si>
-  <si>
-    <t>-0,079329248</t>
-  </si>
-  <si>
-    <t>0,13631405</t>
-  </si>
-  <si>
-    <t>0,072535741</t>
-  </si>
-  <si>
     <t>0,24199004</t>
   </si>
   <si>
-    <t>0,62207635</t>
-  </si>
-  <si>
-    <t>-2,1434005</t>
-  </si>
-  <si>
-    <t>0,52902862</t>
-  </si>
-  <si>
     <t>0,025546699</t>
   </si>
   <si>
-    <t>3,1209291</t>
-  </si>
-  <si>
-    <t>0,50334345</t>
-  </si>
-  <si>
-    <t>0,60840649</t>
-  </si>
-  <si>
-    <t>1,0890312</t>
-  </si>
-  <si>
-    <t>0,058110555</t>
-  </si>
-  <si>
-    <t>0,060498913</t>
-  </si>
-  <si>
-    <t>0,21631323</t>
-  </si>
-  <si>
-    <t>0,80888119</t>
-  </si>
-  <si>
-    <t>0,33202361</t>
-  </si>
-  <si>
-    <t>0,13300926</t>
-  </si>
-  <si>
-    <t>3,9648089</t>
-  </si>
-  <si>
     <t>0,14412117</t>
   </si>
   <si>
-    <t>0,63607223</t>
-  </si>
-  <si>
-    <t>-0,28908582</t>
-  </si>
-  <si>
-    <t>0,70087462</t>
-  </si>
-  <si>
-    <t>1,9676106</t>
-  </si>
-  <si>
-    <t>0,11345209</t>
-  </si>
-  <si>
     <t>5,3130503</t>
   </si>
   <si>
-    <t>-2,0711477</t>
-  </si>
-  <si>
-    <t>0,37410289</t>
-  </si>
-  <si>
-    <t>0,84157121</t>
-  </si>
-  <si>
-    <t>0,36058011</t>
-  </si>
-  <si>
-    <t>0,87385082</t>
-  </si>
-  <si>
-    <t>0,23347617</t>
-  </si>
-  <si>
-    <t>1,3422763</t>
-  </si>
-  <si>
-    <t>1,7410917</t>
-  </si>
-  <si>
-    <t>0,076373752</t>
-  </si>
-  <si>
     <t>0,18183269</t>
   </si>
   <si>
-    <t>0,17885438</t>
-  </si>
-  <si>
     <t>1 kg crop: MANI | category: transitory | summary: strategy_3 (del proyecto Ecuador_needs)</t>
   </si>
   <si>
@@ -2313,15 +1791,6 @@
     <t>crop: ZAPALLO (CALABAZA) | category: transitory | summary: strategy_3</t>
   </si>
   <si>
-    <t>3,688335</t>
-  </si>
-  <si>
-    <t>-10,117683</t>
-  </si>
-  <si>
-    <t>0,79376818</t>
-  </si>
-  <si>
     <t>0,58349273</t>
   </si>
   <si>
@@ -2331,198 +1800,45 @@
     <t>0,18877021</t>
   </si>
   <si>
-    <t>0,22444368</t>
-  </si>
-  <si>
-    <t>0,10209339</t>
-  </si>
-  <si>
     <t>0,78868864</t>
   </si>
   <si>
-    <t>0,53567872</t>
-  </si>
-  <si>
-    <t>0,64824713</t>
-  </si>
-  <si>
-    <t>0,53067631</t>
-  </si>
-  <si>
-    <t>0,32867819</t>
-  </si>
-  <si>
-    <t>0,19303943</t>
-  </si>
-  <si>
-    <t>0,63834749</t>
-  </si>
-  <si>
-    <t>0,23847531</t>
-  </si>
-  <si>
     <t>0,27496729</t>
   </si>
   <si>
-    <t>0,10525497</t>
-  </si>
-  <si>
-    <t>0,49846287</t>
-  </si>
-  <si>
-    <t>0,47793251</t>
-  </si>
-  <si>
-    <t>0,94986794</t>
-  </si>
-  <si>
-    <t>-1,0349011</t>
-  </si>
-  <si>
     <t>0,59367968</t>
   </si>
   <si>
     <t>0,10331103</t>
   </si>
   <si>
-    <t>0,20378457</t>
-  </si>
-  <si>
-    <t>0,1538929</t>
-  </si>
-  <si>
-    <t>0,17145007</t>
-  </si>
-  <si>
-    <t>0,4603766</t>
-  </si>
-  <si>
-    <t>1,077301</t>
-  </si>
-  <si>
-    <t>0,90367644</t>
-  </si>
-  <si>
     <t>8,2616238</t>
   </si>
   <si>
     <t>0,51690267</t>
   </si>
   <si>
-    <t>0,43793054</t>
-  </si>
-  <si>
-    <t>0,24047379</t>
-  </si>
-  <si>
-    <t>0,3253095</t>
-  </si>
-  <si>
-    <t>0,38652546</t>
-  </si>
-  <si>
-    <t>0,11728439</t>
-  </si>
-  <si>
-    <t>1,2235295</t>
-  </si>
-  <si>
-    <t>0,52372337</t>
-  </si>
-  <si>
-    <t>3,2658557</t>
-  </si>
-  <si>
     <t>-0,41494575</t>
   </si>
   <si>
-    <t>0,3208442</t>
-  </si>
-  <si>
-    <t>0,28299165</t>
-  </si>
-  <si>
-    <t>0,12783644</t>
-  </si>
-  <si>
-    <t>0,096668108</t>
-  </si>
-  <si>
     <t>0,38197119</t>
   </si>
   <si>
     <t>0,13227761</t>
   </si>
   <si>
-    <t>1,9424889</t>
-  </si>
-  <si>
-    <t>-0,23245767</t>
-  </si>
-  <si>
-    <t>3,2929047</t>
-  </si>
-  <si>
-    <t>0,40380423</t>
-  </si>
-  <si>
     <t>0,14755391</t>
   </si>
   <si>
-    <t>0,45396216</t>
-  </si>
-  <si>
-    <t>0,0024969234</t>
-  </si>
-  <si>
     <t>0,079840432</t>
   </si>
   <si>
-    <t>2,4492597</t>
-  </si>
-  <si>
     <t>0,25663613</t>
   </si>
   <si>
-    <t>0,60851877</t>
-  </si>
-  <si>
-    <t>0,055858194</t>
-  </si>
-  <si>
     <t>0,045408775</t>
   </si>
   <si>
-    <t>1,0852727</t>
-  </si>
-  <si>
-    <t>0,82195005</t>
-  </si>
-  <si>
-    <t>1,9008184</t>
-  </si>
-  <si>
-    <t>1,8438346</t>
-  </si>
-  <si>
-    <t>0,13067778</t>
-  </si>
-  <si>
-    <t>0,13711746</t>
-  </si>
-  <si>
-    <t>1,2209786</t>
-  </si>
-  <si>
-    <t>2,1275387</t>
-  </si>
-  <si>
-    <t>-5,4302576</t>
-  </si>
-  <si>
-    <t>0,49103283</t>
-  </si>
-  <si>
     <t>-0,036894244</t>
   </si>
   <si>
@@ -2532,198 +1848,45 @@
     <t>0,095586055</t>
   </si>
   <si>
-    <t>0,054821474</t>
-  </si>
-  <si>
-    <t>0,13065015</t>
-  </si>
-  <si>
     <t>0,41266828</t>
   </si>
   <si>
-    <t>0,36557387</t>
-  </si>
-  <si>
-    <t>0,39182978</t>
-  </si>
-  <si>
-    <t>-0,28579638</t>
-  </si>
-  <si>
-    <t>0,085033368</t>
-  </si>
-  <si>
-    <t>0,10726363</t>
-  </si>
-  <si>
-    <t>0,38028505</t>
-  </si>
-  <si>
-    <t>0,11080726</t>
-  </si>
-  <si>
     <t>-0,00073202866</t>
   </si>
   <si>
-    <t>0,07223373</t>
-  </si>
-  <si>
-    <t>0,17037664</t>
-  </si>
-  <si>
-    <t>0,24785947</t>
-  </si>
-  <si>
-    <t>0,19796305</t>
-  </si>
-  <si>
-    <t>-0,60482859</t>
-  </si>
-  <si>
     <t>0,1377962</t>
   </si>
   <si>
     <t>0,027515715</t>
   </si>
   <si>
-    <t>0,12228101</t>
-  </si>
-  <si>
-    <t>0,087886198</t>
-  </si>
-  <si>
-    <t>0,021469781</t>
-  </si>
-  <si>
-    <t>0,29410211</t>
-  </si>
-  <si>
-    <t>0,72590547</t>
-  </si>
-  <si>
-    <t>0,39728772</t>
-  </si>
-  <si>
     <t>2,6474796</t>
   </si>
   <si>
     <t>0,060008824</t>
   </si>
   <si>
-    <t>0,18051195</t>
-  </si>
-  <si>
-    <t>0,12267079</t>
-  </si>
-  <si>
-    <t>0,19090412</t>
-  </si>
-  <si>
-    <t>0,22814236</t>
-  </si>
-  <si>
-    <t>0,030270847</t>
-  </si>
-  <si>
-    <t>0,066604707</t>
-  </si>
-  <si>
-    <t>0,43133372</t>
-  </si>
-  <si>
-    <t>1,8816186</t>
-  </si>
-  <si>
     <t>-0,41461795</t>
   </si>
   <si>
-    <t>0,038257845</t>
-  </si>
-  <si>
-    <t>0,12686519</t>
-  </si>
-  <si>
-    <t>0,01664769</t>
-  </si>
-  <si>
-    <t>0,057297805</t>
-  </si>
-  <si>
     <t>-0,0010168986</t>
   </si>
   <si>
     <t>0,056647215</t>
   </si>
   <si>
-    <t>1,1153583</t>
-  </si>
-  <si>
-    <t>-0,24828723</t>
-  </si>
-  <si>
-    <t>1,6465665</t>
-  </si>
-  <si>
-    <t>0,072249476</t>
-  </si>
-  <si>
     <t>0,044646052</t>
   </si>
   <si>
-    <t>0,18194588</t>
-  </si>
-  <si>
-    <t>-0,010450311</t>
-  </si>
-  <si>
     <t>0,035512439</t>
   </si>
   <si>
-    <t>1,3781592</t>
-  </si>
-  <si>
     <t>-0,00068322675</t>
   </si>
   <si>
-    <t>0,34861636</t>
-  </si>
-  <si>
-    <t>-0,03454335</t>
-  </si>
-  <si>
     <t>-0,044601632</t>
   </si>
   <si>
-    <t>0,61351236</t>
-  </si>
-  <si>
-    <t>0,14902644</t>
-  </si>
-  <si>
-    <t>0,36525002</t>
-  </si>
-  <si>
-    <t>0,98639378</t>
-  </si>
-  <si>
-    <t>0,043144433</t>
-  </si>
-  <si>
-    <t>0,059400843</t>
-  </si>
-  <si>
-    <t>0,63407262</t>
-  </si>
-  <si>
-    <t>1,5607963</t>
-  </si>
-  <si>
-    <t>-4,687425</t>
-  </si>
-  <si>
-    <t>0,30273535</t>
-  </si>
-  <si>
     <t>0,62038698</t>
   </si>
   <si>
@@ -2733,187 +1896,1015 @@
     <t>0,093184152</t>
   </si>
   <si>
-    <t>0,16962221</t>
-  </si>
-  <si>
-    <t>-0,028556766</t>
-  </si>
-  <si>
     <t>0,37602036</t>
   </si>
   <si>
-    <t>0,17010485</t>
-  </si>
-  <si>
-    <t>0,25641734</t>
-  </si>
-  <si>
-    <t>0,81647268</t>
-  </si>
-  <si>
-    <t>0,24364483</t>
-  </si>
-  <si>
-    <t>0,085775797</t>
-  </si>
-  <si>
-    <t>0,25806244</t>
-  </si>
-  <si>
-    <t>0,12766806</t>
-  </si>
-  <si>
     <t>0,27569931</t>
   </si>
   <si>
-    <t>0,033021235</t>
-  </si>
-  <si>
-    <t>0,32808623</t>
-  </si>
-  <si>
-    <t>0,23007304</t>
-  </si>
-  <si>
-    <t>0,75190489</t>
-  </si>
-  <si>
-    <t>-0,43007254</t>
-  </si>
-  <si>
     <t>0,45588348</t>
   </si>
   <si>
     <t>0,075795316</t>
   </si>
   <si>
-    <t>0,081503555</t>
-  </si>
-  <si>
-    <t>0,066006699</t>
-  </si>
-  <si>
-    <t>0,14998029</t>
-  </si>
-  <si>
-    <t>0,16627448</t>
-  </si>
-  <si>
-    <t>0,35139549</t>
-  </si>
-  <si>
-    <t>0,50638872</t>
-  </si>
-  <si>
     <t>5,6141442</t>
   </si>
   <si>
     <t>0,45689385</t>
   </si>
   <si>
-    <t>0,25741858</t>
-  </si>
-  <si>
-    <t>0,117803</t>
-  </si>
-  <si>
-    <t>0,13440537</t>
-  </si>
-  <si>
-    <t>0,1583831</t>
-  </si>
-  <si>
-    <t>0,087013542</t>
-  </si>
-  <si>
-    <t>1,1569248</t>
-  </si>
-  <si>
-    <t>0,092389648</t>
-  </si>
-  <si>
-    <t>1,3842371</t>
-  </si>
-  <si>
     <t>-0,00032779872</t>
   </si>
   <si>
-    <t>0,28258635</t>
-  </si>
-  <si>
-    <t>0,15612645</t>
-  </si>
-  <si>
-    <t>0,11118875</t>
-  </si>
-  <si>
-    <t>0,039370304</t>
-  </si>
-  <si>
     <t>0,38298809</t>
   </si>
   <si>
     <t>0,075630394</t>
   </si>
   <si>
-    <t>0,82713061</t>
-  </si>
-  <si>
-    <t>0,015829552</t>
-  </si>
-  <si>
-    <t>1,6463382</t>
-  </si>
-  <si>
-    <t>0,33155476</t>
-  </si>
-  <si>
     <t>0,10290786</t>
   </si>
   <si>
-    <t>0,27201628</t>
-  </si>
-  <si>
-    <t>0,012947234</t>
-  </si>
-  <si>
     <t>0,044327994</t>
   </si>
   <si>
-    <t>1,0711005</t>
-  </si>
-  <si>
     <t>0,25731936</t>
   </si>
   <si>
-    <t>0,25990241</t>
-  </si>
-  <si>
-    <t>0,090401544</t>
-  </si>
-  <si>
     <t>0,090010407</t>
   </si>
   <si>
-    <t>0,47176034</t>
-  </si>
-  <si>
-    <t>0,6729236</t>
-  </si>
-  <si>
-    <t>1,5355684</t>
-  </si>
-  <si>
-    <t>0,85744083</t>
-  </si>
-  <si>
-    <t>0,08753335</t>
-  </si>
-  <si>
-    <t>0,07771662</t>
-  </si>
-  <si>
-    <t>0,58690598</t>
+    <t>0,30535711</t>
+  </si>
+  <si>
+    <t>1,0702526</t>
+  </si>
+  <si>
+    <t>0,38056231</t>
+  </si>
+  <si>
+    <t>0,31784239</t>
+  </si>
+  <si>
+    <t>0,5539558</t>
+  </si>
+  <si>
+    <t>0,46444256</t>
+  </si>
+  <si>
+    <t>0,79133731</t>
+  </si>
+  <si>
+    <t>6,0817408</t>
+  </si>
+  <si>
+    <t>2,1184361</t>
+  </si>
+  <si>
+    <t>0,97485486</t>
+  </si>
+  <si>
+    <t>1,434705</t>
+  </si>
+  <si>
+    <t>0,1500067</t>
+  </si>
+  <si>
+    <t>0,078965332</t>
+  </si>
+  <si>
+    <t>0,10137209</t>
+  </si>
+  <si>
+    <t>0,28383613</t>
+  </si>
+  <si>
+    <t>7,212029</t>
+  </si>
+  <si>
+    <t>18,70433</t>
+  </si>
+  <si>
+    <t>0,097033535</t>
+  </si>
+  <si>
+    <t>0,52590079</t>
+  </si>
+  <si>
+    <t>2,3173177</t>
+  </si>
+  <si>
+    <t>1,7732449</t>
+  </si>
+  <si>
+    <t>1,8983955</t>
+  </si>
+  <si>
+    <t>0,33427619</t>
+  </si>
+  <si>
+    <t>0,19241676</t>
+  </si>
+  <si>
+    <t>0,80599154</t>
+  </si>
+  <si>
+    <t>0,87439326</t>
+  </si>
+  <si>
+    <t>0,98520543</t>
+  </si>
+  <si>
+    <t>0,67447215</t>
+  </si>
+  <si>
+    <t>0,57542023</t>
+  </si>
+  <si>
+    <t>0,73301816</t>
+  </si>
+  <si>
+    <t>0,58471658</t>
+  </si>
+  <si>
+    <t>1,2528753</t>
+  </si>
+  <si>
+    <t>5,7402897</t>
+  </si>
+  <si>
+    <t>0,72872349</t>
+  </si>
+  <si>
+    <t>1,1868082</t>
+  </si>
+  <si>
+    <t>2,0806655</t>
+  </si>
+  <si>
+    <t>0,23655592</t>
+  </si>
+  <si>
+    <t>0,14918843</t>
+  </si>
+  <si>
+    <t>0,66388111</t>
+  </si>
+  <si>
+    <t>3,4090127</t>
+  </si>
+  <si>
+    <t>0,61468039</t>
+  </si>
+  <si>
+    <t>0,10812093</t>
+  </si>
+  <si>
+    <t>8,7971892</t>
+  </si>
+  <si>
+    <t>1,5411816</t>
+  </si>
+  <si>
+    <t>0,28462662</t>
+  </si>
+  <si>
+    <t>0,68944249</t>
+  </si>
+  <si>
+    <t>2,1204489</t>
+  </si>
+  <si>
+    <t>0,67436821</t>
+  </si>
+  <si>
+    <t>-1,0138718</t>
+  </si>
+  <si>
+    <t>1,1436466</t>
+  </si>
+  <si>
+    <t>2,1713646</t>
+  </si>
+  <si>
+    <t>0,88288984</t>
+  </si>
+  <si>
+    <t>0,84468834</t>
+  </si>
+  <si>
+    <t>1,1627792</t>
+  </si>
+  <si>
+    <t>3,3522992</t>
+  </si>
+  <si>
+    <t>4,1602189</t>
+  </si>
+  <si>
+    <t>0,42364289</t>
+  </si>
+  <si>
+    <t>0,4772052</t>
+  </si>
+  <si>
+    <t>0,042984693</t>
+  </si>
+  <si>
+    <t>0,71347501</t>
+  </si>
+  <si>
+    <t>0,2259054</t>
+  </si>
+  <si>
+    <t>0,17888352</t>
+  </si>
+  <si>
+    <t>0,28683524</t>
+  </si>
+  <si>
+    <t>0,28417823</t>
+  </si>
+  <si>
+    <t>0,44142552</t>
+  </si>
+  <si>
+    <t>3,4724698</t>
+  </si>
+  <si>
+    <t>1,0634421</t>
+  </si>
+  <si>
+    <t>0,13910468</t>
+  </si>
+  <si>
+    <t>0,85035127</t>
+  </si>
+  <si>
+    <t>0,086488587</t>
+  </si>
+  <si>
+    <t>0,068184478</t>
+  </si>
+  <si>
+    <t>0,059994199</t>
+  </si>
+  <si>
+    <t>0,15601651</t>
+  </si>
+  <si>
+    <t>4,8484382</t>
+  </si>
+  <si>
+    <t>12,523881</t>
+  </si>
+  <si>
+    <t>0,076318703</t>
+  </si>
+  <si>
+    <t>0,40582705</t>
+  </si>
+  <si>
+    <t>1,3399495</t>
+  </si>
+  <si>
+    <t>0,99613204</t>
+  </si>
+  <si>
+    <t>0,95346568</t>
+  </si>
+  <si>
+    <t>0,15346593</t>
+  </si>
+  <si>
+    <t>0,099551743</t>
+  </si>
+  <si>
+    <t>0,41813239</t>
+  </si>
+  <si>
+    <t>0,45252473</t>
+  </si>
+  <si>
+    <t>0,68260321</t>
+  </si>
+  <si>
+    <t>0,34642131</t>
+  </si>
+  <si>
+    <t>0,30146087</t>
+  </si>
+  <si>
+    <t>0,14479707</t>
+  </si>
+  <si>
+    <t>0,34742172</t>
+  </si>
+  <si>
+    <t>0,73159657</t>
+  </si>
+  <si>
+    <t>2,8653068</t>
+  </si>
+  <si>
+    <t>0,36348063</t>
+  </si>
+  <si>
+    <t>0,58699465</t>
+  </si>
+  <si>
+    <t>1,002473</t>
+  </si>
+  <si>
+    <t>0,14699462</t>
+  </si>
+  <si>
+    <t>0,089770105</t>
+  </si>
+  <si>
+    <t>0,41505589</t>
+  </si>
+  <si>
+    <t>2,556683</t>
+  </si>
+  <si>
+    <t>0,40895117</t>
+  </si>
+  <si>
+    <t>0,029240334</t>
+  </si>
+  <si>
+    <t>5,0271105</t>
+  </si>
+  <si>
+    <t>0,8420344</t>
+  </si>
+  <si>
+    <t>0,099781248</t>
+  </si>
+  <si>
+    <t>-0,00038408114</t>
+  </si>
+  <si>
+    <t>0,32469683</t>
+  </si>
+  <si>
+    <t>0,34525461</t>
+  </si>
+  <si>
+    <t>-0,83507186</t>
+  </si>
+  <si>
+    <t>0,7739639</t>
+  </si>
+  <si>
+    <t>1,2630928</t>
+  </si>
+  <si>
+    <t>0,52105673</t>
+  </si>
+  <si>
+    <t>0,0052092144</t>
+  </si>
+  <si>
+    <t>0,68595258</t>
+  </si>
+  <si>
+    <t>1,9903754</t>
+  </si>
+  <si>
+    <t>2,5331903</t>
+  </si>
+  <si>
+    <t>0,28359711</t>
+  </si>
+  <si>
+    <t>0,30153168</t>
+  </si>
+  <si>
+    <t>0,26237242</t>
+  </si>
+  <si>
+    <t>0,35677756</t>
+  </si>
+  <si>
+    <t>0,15465692</t>
+  </si>
+  <si>
+    <t>0,13895887</t>
+  </si>
+  <si>
+    <t>0,26712056</t>
+  </si>
+  <si>
+    <t>0,18026433</t>
+  </si>
+  <si>
+    <t>0,34991179</t>
+  </si>
+  <si>
+    <t>2,609271</t>
+  </si>
+  <si>
+    <t>1,054994</t>
+  </si>
+  <si>
+    <t>0,83575018</t>
+  </si>
+  <si>
+    <t>0,58435378</t>
+  </si>
+  <si>
+    <t>0,063518117</t>
+  </si>
+  <si>
+    <t>0,010780854</t>
+  </si>
+  <si>
+    <t>0,041377894</t>
+  </si>
+  <si>
+    <t>0,12781962</t>
+  </si>
+  <si>
+    <t>2,3635908</t>
+  </si>
+  <si>
+    <t>6,1804497</t>
+  </si>
+  <si>
+    <t>0,020714832</t>
+  </si>
+  <si>
+    <t>0,12007374</t>
+  </si>
+  <si>
+    <t>0,9773682</t>
+  </si>
+  <si>
+    <t>0,77711286</t>
+  </si>
+  <si>
+    <t>0,94492985</t>
+  </si>
+  <si>
+    <t>0,18081026</t>
+  </si>
+  <si>
+    <t>0,092865019</t>
+  </si>
+  <si>
+    <t>0,38785915</t>
+  </si>
+  <si>
+    <t>0,42186852</t>
+  </si>
+  <si>
+    <t>0,30260222</t>
+  </si>
+  <si>
+    <t>0,32805084</t>
+  </si>
+  <si>
+    <t>0,27395936</t>
+  </si>
+  <si>
+    <t>0,5882211</t>
+  </si>
+  <si>
+    <t>0,23729487</t>
+  </si>
+  <si>
+    <t>0,52127874</t>
+  </si>
+  <si>
+    <t>2,8749828</t>
+  </si>
+  <si>
+    <t>0,36524286</t>
+  </si>
+  <si>
+    <t>0,59981356</t>
+  </si>
+  <si>
+    <t>1,0781926</t>
+  </si>
+  <si>
+    <t>0,089561294</t>
+  </si>
+  <si>
+    <t>0,059418325</t>
+  </si>
+  <si>
+    <t>0,24882523</t>
+  </si>
+  <si>
+    <t>0,85232964</t>
+  </si>
+  <si>
+    <t>0,20572923</t>
+  </si>
+  <si>
+    <t>0,078880597</t>
+  </si>
+  <si>
+    <t>3,7700787</t>
+  </si>
+  <si>
+    <t>0,69914721</t>
+  </si>
+  <si>
+    <t>0,18484537</t>
+  </si>
+  <si>
+    <t>0,68982657</t>
+  </si>
+  <si>
+    <t>1,7957521</t>
+  </si>
+  <si>
+    <t>0,3291136</t>
+  </si>
+  <si>
+    <t>-0,17879993</t>
+  </si>
+  <si>
+    <t>0,36968272</t>
+  </si>
+  <si>
+    <t>0,90827185</t>
+  </si>
+  <si>
+    <t>0,36183311</t>
+  </si>
+  <si>
+    <t>0,83947912</t>
+  </si>
+  <si>
+    <t>0,47682659</t>
+  </si>
+  <si>
+    <t>1,3619238</t>
+  </si>
+  <si>
+    <t>1,6270286</t>
+  </si>
+  <si>
+    <t>0,14004578</t>
+  </si>
+  <si>
+    <t>0,17567352</t>
+  </si>
+  <si>
+    <t>3,6929481</t>
+  </si>
+  <si>
+    <t>1,4586145</t>
+  </si>
+  <si>
+    <t>0,79241484</t>
+  </si>
+  <si>
+    <t>0,21172365</t>
+  </si>
+  <si>
+    <t>0,74962294</t>
+  </si>
+  <si>
+    <t>0,586264</t>
+  </si>
+  <si>
+    <t>0,62803306</t>
+  </si>
+  <si>
+    <t>0,37961127</t>
+  </si>
+  <si>
+    <t>0,32568237</t>
+  </si>
+  <si>
+    <t>0,2106995</t>
+  </si>
+  <si>
+    <t>0,73789068</t>
+  </si>
+  <si>
+    <t>0,85440289</t>
+  </si>
+  <si>
+    <t>0,20926895</t>
+  </si>
+  <si>
+    <t>0,53157333</t>
+  </si>
+  <si>
+    <t>0,60268647</t>
+  </si>
+  <si>
+    <t>0,70149394</t>
+  </si>
+  <si>
+    <t>0,17167647</t>
+  </si>
+  <si>
+    <t>0,24737329</t>
+  </si>
+  <si>
+    <t>0,16565359</t>
+  </si>
+  <si>
+    <t>0,16227798</t>
+  </si>
+  <si>
+    <t>0,42439709</t>
+  </si>
+  <si>
+    <t>1,0364315</t>
+  </si>
+  <si>
+    <t>3,0767016</t>
+  </si>
+  <si>
+    <t>0,36750605</t>
+  </si>
+  <si>
+    <t>0,28475149</t>
+  </si>
+  <si>
+    <t>0,30572179</t>
+  </si>
+  <si>
+    <t>0,36359049</t>
+  </si>
+  <si>
+    <t>0,1074746</t>
+  </si>
+  <si>
+    <t>0,70019128</t>
+  </si>
+  <si>
+    <t>0,52053481</t>
+  </si>
+  <si>
+    <t>3,1996868</t>
+  </si>
+  <si>
+    <t>0,29566115</t>
+  </si>
+  <si>
+    <t>0,89869784</t>
+  </si>
+  <si>
+    <t>0,11859951</t>
+  </si>
+  <si>
+    <t>0,096301988</t>
+  </si>
+  <si>
+    <t>1,9380133</t>
+  </si>
+  <si>
+    <t>3,2794158</t>
+  </si>
+  <si>
+    <t>0,16834913</t>
+  </si>
+  <si>
+    <t>0,3939445</t>
+  </si>
+  <si>
+    <t>0,11020605</t>
+  </si>
+  <si>
+    <t>2,3434028</t>
+  </si>
+  <si>
+    <t>0,58547404</t>
+  </si>
+  <si>
+    <t>0,11503631</t>
+  </si>
+  <si>
+    <t>0,99997673</t>
+  </si>
+  <si>
+    <t>0,32872957</t>
+  </si>
+  <si>
+    <t>1,429814</t>
+  </si>
+  <si>
+    <t>1,6980162</t>
+  </si>
+  <si>
+    <t>0,68930514</t>
+  </si>
+  <si>
+    <t>0,10998327</t>
+  </si>
+  <si>
+    <t>1,2200392</t>
+  </si>
+  <si>
+    <t>2,130523</t>
+  </si>
+  <si>
+    <t>0,94311215</t>
+  </si>
+  <si>
+    <t>0,49297563</t>
+  </si>
+  <si>
+    <t>0,052126527</t>
+  </si>
+  <si>
+    <t>0,50386794</t>
+  </si>
+  <si>
+    <t>0,39486474</t>
+  </si>
+  <si>
+    <t>0,39370241</t>
+  </si>
+  <si>
+    <t>-0,19075554</t>
+  </si>
+  <si>
+    <t>0,084398653</t>
+  </si>
+  <si>
+    <t>0,12181365</t>
+  </si>
+  <si>
+    <t>0,45006</t>
+  </si>
+  <si>
+    <t>0,48882911</t>
+  </si>
+  <si>
+    <t>0,1326141</t>
+  </si>
+  <si>
+    <t>0,19194022</t>
+  </si>
+  <si>
+    <t>0,33475556</t>
+  </si>
+  <si>
+    <t>0,1480323</t>
+  </si>
+  <si>
+    <t>0,05864336</t>
+  </si>
+  <si>
+    <t>0,14772396</t>
+  </si>
+  <si>
+    <t>0,097243148</t>
+  </si>
+  <si>
+    <t>0,021201147</t>
+  </si>
+  <si>
+    <t>0,28647927</t>
+  </si>
+  <si>
+    <t>0,72020648</t>
+  </si>
+  <si>
+    <t>1,5976488</t>
+  </si>
+  <si>
+    <t>0,16647295</t>
+  </si>
+  <si>
+    <t>0,15404074</t>
+  </si>
+  <si>
+    <t>0,19159642</t>
+  </si>
+  <si>
+    <t>0,22757219</t>
+  </si>
+  <si>
+    <t>0,028192483</t>
+  </si>
+  <si>
+    <t>-0,044273093</t>
+  </si>
+  <si>
+    <t>0,4326719</t>
+  </si>
+  <si>
+    <t>1,8693944</t>
+  </si>
+  <si>
+    <t>0,034283768</t>
+  </si>
+  <si>
+    <t>0,46542923</t>
+  </si>
+  <si>
+    <t>0,014690694</t>
+  </si>
+  <si>
+    <t>0,057294554</t>
+  </si>
+  <si>
+    <t>1,1152272</t>
+  </si>
+  <si>
+    <t>1,6882199</t>
+  </si>
+  <si>
+    <t>0,022364443</t>
+  </si>
+  <si>
+    <t>0,17023493</t>
+  </si>
+  <si>
+    <t>0,049447713</t>
+  </si>
+  <si>
+    <t>1,3578275</t>
+  </si>
+  <si>
+    <t>0,34373395</t>
+  </si>
+  <si>
+    <t>0,0010609036</t>
+  </si>
+  <si>
+    <t>0,595441</t>
+  </si>
+  <si>
+    <t>0,09476833</t>
+  </si>
+  <si>
+    <t>0,26545999</t>
+  </si>
+  <si>
+    <t>0,9731865</t>
+  </si>
+  <si>
+    <t>0,38348982</t>
+  </si>
+  <si>
+    <t>0,05641587</t>
+  </si>
+  <si>
+    <t>0,63404511</t>
+  </si>
+  <si>
+    <t>1,5624251</t>
+  </si>
+  <si>
+    <t>0,51550236</t>
+  </si>
+  <si>
+    <t>0,2994392</t>
+  </si>
+  <si>
+    <t>0,15959713</t>
+  </si>
+  <si>
+    <t>0,245755</t>
+  </si>
+  <si>
+    <t>0,19139926</t>
+  </si>
+  <si>
+    <t>0,23433065</t>
+  </si>
+  <si>
+    <t>0,57036681</t>
+  </si>
+  <si>
+    <t>0,24128372</t>
+  </si>
+  <si>
+    <t>0,088885847</t>
+  </si>
+  <si>
+    <t>0,28783068</t>
+  </si>
+  <si>
+    <t>0,36557378</t>
+  </si>
+  <si>
+    <t>0,076654854</t>
+  </si>
+  <si>
+    <t>0,33963311</t>
+  </si>
+  <si>
+    <t>0,26793091</t>
+  </si>
+  <si>
+    <t>0,55346164</t>
+  </si>
+  <si>
+    <t>0,11303311</t>
+  </si>
+  <si>
+    <t>0,099649331</t>
+  </si>
+  <si>
+    <t>0,068410441</t>
+  </si>
+  <si>
+    <t>0,14107683</t>
+  </si>
+  <si>
+    <t>0,13791783</t>
+  </si>
+  <si>
+    <t>0,31622502</t>
+  </si>
+  <si>
+    <t>1,4790528</t>
+  </si>
+  <si>
+    <t>0,2010331</t>
+  </si>
+  <si>
+    <t>0,13071075</t>
+  </si>
+  <si>
+    <t>0,11412537</t>
+  </si>
+  <si>
+    <t>0,1360183</t>
+  </si>
+  <si>
+    <t>0,079282119</t>
+  </si>
+  <si>
+    <t>0,74446437</t>
+  </si>
+  <si>
+    <t>0,087862914</t>
+  </si>
+  <si>
+    <t>1,3302924</t>
+  </si>
+  <si>
+    <t>0,26137738</t>
+  </si>
+  <si>
+    <t>0,43326861</t>
+  </si>
+  <si>
+    <t>0,10390882</t>
+  </si>
+  <si>
+    <t>0,039007433</t>
+  </si>
+  <si>
+    <t>0,82278611</t>
+  </si>
+  <si>
+    <t>1,5911959</t>
+  </si>
+  <si>
+    <t>0,14598468</t>
+  </si>
+  <si>
+    <t>0,22370957</t>
+  </si>
+  <si>
+    <t>0,060758339</t>
+  </si>
+  <si>
+    <t>0,98557525</t>
+  </si>
+  <si>
+    <t>0,24174009</t>
+  </si>
+  <si>
+    <t>0,11397541</t>
+  </si>
+  <si>
+    <t>0,40453572</t>
+  </si>
+  <si>
+    <t>0,23396124</t>
+  </si>
+  <si>
+    <t>1,164354</t>
+  </si>
+  <si>
+    <t>0,72482971</t>
+  </si>
+  <si>
+    <t>0,30581532</t>
+  </si>
+  <si>
+    <t>0,053567401</t>
+  </si>
+  <si>
+    <t>0,5859941</t>
   </si>
 </sst>
 </file>
@@ -3242,12 +3233,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:W32"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -3261,7 +3252,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -3275,7 +3266,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -3289,7 +3280,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -3303,7 +3294,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -3317,7 +3308,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -3331,7 +3322,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -3345,7 +3336,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -3359,7 +3350,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -3373,7 +3364,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>45</v>
       </c>
@@ -3387,7 +3378,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>47</v>
       </c>
@@ -3401,7 +3392,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>49</v>
       </c>
@@ -3415,7 +3406,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>51</v>
       </c>
@@ -3429,7 +3420,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>53</v>
       </c>
@@ -3443,7 +3434,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>55</v>
       </c>
@@ -3451,7 +3442,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>57</v>
       </c>
@@ -3474,7 +3465,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>59</v>
       </c>
@@ -3497,7 +3488,7 @@
         <v>1.8339487000000001</v>
       </c>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -3520,7 +3511,7 @@
         <v>1.3648765</v>
       </c>
     </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>20</v>
       </c>
@@ -3543,7 +3534,7 @@
         <v>0.46907212999999998</v>
       </c>
     </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -3551,7 +3542,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -3559,7 +3550,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>26</v>
       </c>
@@ -3567,7 +3558,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>27</v>
       </c>
@@ -3575,7 +3566,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>28</v>
       </c>
@@ -3583,7 +3574,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>29</v>
       </c>
@@ -3591,7 +3582,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>31</v>
       </c>
@@ -3599,7 +3590,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>30</v>
       </c>
@@ -3652,7 +3643,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>41</v>
       </c>
@@ -3705,7 +3696,7 @@
         <v>37.106980999999998</v>
       </c>
     </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>43</v>
       </c>
@@ -3758,7 +3749,7 @@
         <v>21.34233</v>
       </c>
     </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>44</v>
       </c>
@@ -3819,19 +3810,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36E204EE-76B8-4235-9713-7B898C2D2B41}">
   <dimension ref="A1:AA28"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -3845,7 +3836,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -3859,7 +3850,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -3873,7 +3864,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -3887,7 +3878,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -3901,7 +3892,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -3915,7 +3906,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -3929,7 +3920,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -3943,7 +3934,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -3957,7 +3948,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>45</v>
       </c>
@@ -3971,7 +3962,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>47</v>
       </c>
@@ -3985,7 +3976,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -3999,7 +3990,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>20</v>
       </c>
@@ -4013,7 +4004,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>22</v>
       </c>
@@ -4027,7 +4018,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>24</v>
       </c>
@@ -4041,7 +4032,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>26</v>
       </c>
@@ -4055,7 +4046,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>27</v>
       </c>
@@ -4069,7 +4060,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>28</v>
       </c>
@@ -4083,7 +4074,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>29</v>
       </c>
@@ -4097,7 +4088,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>31</v>
       </c>
@@ -4111,7 +4102,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>30</v>
       </c>
@@ -4179,7 +4170,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>41</v>
       </c>
@@ -4247,7 +4238,7 @@
         <v>6.6520478000000001</v>
       </c>
     </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>43</v>
       </c>
@@ -4315,7 +4306,7 @@
         <v>4.4545519999999996</v>
       </c>
     </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>44</v>
       </c>
@@ -4391,12 +4382,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{653F6E1D-BB0E-4AF1-8D89-E81FDD81ED90}">
   <dimension ref="A2:X20"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.54296875" customWidth="1"/>
+    <col min="1" max="1" width="10.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -4416,7 +4407,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -4436,7 +4427,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -4456,7 +4447,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -4476,7 +4467,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -4496,7 +4487,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -4516,7 +4507,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -4536,7 +4527,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -4556,7 +4547,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -4576,7 +4567,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -4596,7 +4587,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -4616,7 +4607,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -4636,7 +4627,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>29</v>
       </c>
@@ -4656,7 +4647,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>31</v>
       </c>
@@ -4670,7 +4661,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="U16" t="s">
         <v>30</v>
       </c>
@@ -4684,7 +4675,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>30</v>
       </c>
@@ -4728,7 +4719,7 @@
         <v>60.489479000000003</v>
       </c>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>41</v>
       </c>
@@ -4772,7 +4763,7 @@
         <v>30.310210999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>43</v>
       </c>
@@ -4816,7 +4807,7 @@
         <v>30.179268</v>
       </c>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>44</v>
       </c>
@@ -4856,14 +4847,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDB994F4-824A-4F71-A5D5-BE9319DBCD9E}">
   <dimension ref="A1:EP93"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:79" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="3" spans="1:79" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -4871,7 +4862,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:79" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -4879,7 +4870,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:79" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -4887,7 +4878,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="6" spans="1:79" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -4895,7 +4886,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="7" spans="1:79" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -4903,7 +4894,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="8" spans="1:79" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -4911,7 +4902,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="9" spans="1:79" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -4919,7 +4910,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="10" spans="1:79" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -4927,7 +4918,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="11" spans="1:79" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -4941,7 +4932,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:79" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>45</v>
       </c>
@@ -4955,7 +4946,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:79" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>47</v>
       </c>
@@ -4966,10 +4957,10 @@
         <v>4</v>
       </c>
       <c r="CA13" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="14" spans="1:79" x14ac:dyDescent="0.35">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="14" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>49</v>
       </c>
@@ -4980,10 +4971,10 @@
         <v>6</v>
       </c>
       <c r="CA14" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="15" spans="1:79" x14ac:dyDescent="0.35">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="15" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>51</v>
       </c>
@@ -4994,10 +4985,10 @@
         <v>8</v>
       </c>
       <c r="CA15" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="16" spans="1:79" x14ac:dyDescent="0.35">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="16" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>53</v>
       </c>
@@ -5008,10 +4999,10 @@
         <v>10</v>
       </c>
       <c r="CA16" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="17" spans="1:79" x14ac:dyDescent="0.35">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="17" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>55</v>
       </c>
@@ -5022,10 +5013,10 @@
         <v>12</v>
       </c>
       <c r="CA17" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="18" spans="1:79" x14ac:dyDescent="0.35">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="18" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>57</v>
       </c>
@@ -5036,10 +5027,10 @@
         <v>14</v>
       </c>
       <c r="CA18" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="19" spans="1:79" x14ac:dyDescent="0.35">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="19" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>59</v>
       </c>
@@ -5050,10 +5041,10 @@
         <v>16</v>
       </c>
       <c r="CA19" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="20" spans="1:79" x14ac:dyDescent="0.35">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="20" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>148</v>
       </c>
@@ -5064,10 +5055,10 @@
         <v>45</v>
       </c>
       <c r="CA20" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="21" spans="1:79" x14ac:dyDescent="0.35">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="21" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>150</v>
       </c>
@@ -5078,10 +5069,10 @@
         <v>47</v>
       </c>
       <c r="CA21" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="22" spans="1:79" x14ac:dyDescent="0.35">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="22" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>152</v>
       </c>
@@ -5092,10 +5083,10 @@
         <v>49</v>
       </c>
       <c r="CA22" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="23" spans="1:79" x14ac:dyDescent="0.35">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="23" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>154</v>
       </c>
@@ -5106,10 +5097,10 @@
         <v>51</v>
       </c>
       <c r="CA23" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="24" spans="1:79" x14ac:dyDescent="0.35">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="24" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>156</v>
       </c>
@@ -5120,10 +5111,10 @@
         <v>53</v>
       </c>
       <c r="CA24" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="25" spans="1:79" x14ac:dyDescent="0.35">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="25" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>158</v>
       </c>
@@ -5134,10 +5125,10 @@
         <v>55</v>
       </c>
       <c r="CA25" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="26" spans="1:79" x14ac:dyDescent="0.35">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="26" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>160</v>
       </c>
@@ -5148,10 +5139,10 @@
         <v>57</v>
       </c>
       <c r="CA26" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="27" spans="1:79" x14ac:dyDescent="0.35">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="27" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>162</v>
       </c>
@@ -5162,10 +5153,10 @@
         <v>59</v>
       </c>
       <c r="CA27" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="28" spans="1:79" x14ac:dyDescent="0.35">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="28" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>164</v>
       </c>
@@ -5176,10 +5167,10 @@
         <v>148</v>
       </c>
       <c r="CA28" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="29" spans="1:79" x14ac:dyDescent="0.35">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="29" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>166</v>
       </c>
@@ -5190,10 +5181,10 @@
         <v>150</v>
       </c>
       <c r="CA29" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="30" spans="1:79" x14ac:dyDescent="0.35">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="30" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>168</v>
       </c>
@@ -5204,10 +5195,10 @@
         <v>152</v>
       </c>
       <c r="CA30" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="31" spans="1:79" x14ac:dyDescent="0.35">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="31" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>170</v>
       </c>
@@ -5218,10 +5209,10 @@
         <v>154</v>
       </c>
       <c r="CA31" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="32" spans="1:79" x14ac:dyDescent="0.35">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="32" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>172</v>
       </c>
@@ -5232,10 +5223,10 @@
         <v>156</v>
       </c>
       <c r="CA32" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="33" spans="1:79" x14ac:dyDescent="0.35">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="33" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>174</v>
       </c>
@@ -5246,10 +5237,10 @@
         <v>158</v>
       </c>
       <c r="CA33" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="34" spans="1:79" x14ac:dyDescent="0.35">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="34" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>176</v>
       </c>
@@ -5260,10 +5251,10 @@
         <v>160</v>
       </c>
       <c r="CA34" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="35" spans="1:79" x14ac:dyDescent="0.35">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="35" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>178</v>
       </c>
@@ -5274,10 +5265,10 @@
         <v>162</v>
       </c>
       <c r="CA35" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="36" spans="1:79" x14ac:dyDescent="0.35">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="36" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>180</v>
       </c>
@@ -5288,10 +5279,10 @@
         <v>164</v>
       </c>
       <c r="CA36" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="37" spans="1:79" x14ac:dyDescent="0.35">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="37" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>182</v>
       </c>
@@ -5302,10 +5293,10 @@
         <v>166</v>
       </c>
       <c r="CA37" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="38" spans="1:79" x14ac:dyDescent="0.35">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="38" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>184</v>
       </c>
@@ -5316,10 +5307,10 @@
         <v>168</v>
       </c>
       <c r="CA38" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="39" spans="1:79" x14ac:dyDescent="0.35">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="39" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>186</v>
       </c>
@@ -5330,10 +5321,10 @@
         <v>170</v>
       </c>
       <c r="CA39" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="40" spans="1:79" x14ac:dyDescent="0.35">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="40" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>188</v>
       </c>
@@ -5344,10 +5335,10 @@
         <v>172</v>
       </c>
       <c r="CA40" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="41" spans="1:79" x14ac:dyDescent="0.35">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="41" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>190</v>
       </c>
@@ -5358,10 +5349,10 @@
         <v>174</v>
       </c>
       <c r="CA41" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="42" spans="1:79" x14ac:dyDescent="0.35">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="42" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>192</v>
       </c>
@@ -5372,10 +5363,10 @@
         <v>176</v>
       </c>
       <c r="CA42" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="43" spans="1:79" x14ac:dyDescent="0.35">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="43" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>194</v>
       </c>
@@ -5386,10 +5377,10 @@
         <v>178</v>
       </c>
       <c r="CA43" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="44" spans="1:79" x14ac:dyDescent="0.35">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="44" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>196</v>
       </c>
@@ -5400,10 +5391,10 @@
         <v>180</v>
       </c>
       <c r="CA44" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="45" spans="1:79" x14ac:dyDescent="0.35">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="45" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>198</v>
       </c>
@@ -5414,10 +5405,10 @@
         <v>182</v>
       </c>
       <c r="CA45" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="46" spans="1:79" x14ac:dyDescent="0.35">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="46" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>200</v>
       </c>
@@ -5428,10 +5419,10 @@
         <v>184</v>
       </c>
       <c r="CA46" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="47" spans="1:79" x14ac:dyDescent="0.35">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="47" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>202</v>
       </c>
@@ -5442,10 +5433,10 @@
         <v>186</v>
       </c>
       <c r="CA47" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="48" spans="1:79" x14ac:dyDescent="0.35">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="48" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>204</v>
       </c>
@@ -5456,10 +5447,10 @@
         <v>188</v>
       </c>
       <c r="CA48" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="49" spans="1:79" x14ac:dyDescent="0.35">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="49" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>206</v>
       </c>
@@ -5470,10 +5461,10 @@
         <v>190</v>
       </c>
       <c r="CA49" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="50" spans="1:79" x14ac:dyDescent="0.35">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="50" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>208</v>
       </c>
@@ -5484,10 +5475,10 @@
         <v>192</v>
       </c>
       <c r="CA50" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="51" spans="1:79" x14ac:dyDescent="0.35">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="51" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>210</v>
       </c>
@@ -5498,10 +5489,10 @@
         <v>194</v>
       </c>
       <c r="CA51" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="52" spans="1:79" x14ac:dyDescent="0.35">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="52" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>212</v>
       </c>
@@ -5512,10 +5503,10 @@
         <v>196</v>
       </c>
       <c r="CA52" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="53" spans="1:79" x14ac:dyDescent="0.35">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="53" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>214</v>
       </c>
@@ -5526,10 +5517,10 @@
         <v>198</v>
       </c>
       <c r="CA53" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="54" spans="1:79" x14ac:dyDescent="0.35">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="54" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>216</v>
       </c>
@@ -5540,10 +5531,10 @@
         <v>200</v>
       </c>
       <c r="CA54" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="55" spans="1:79" x14ac:dyDescent="0.35">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="55" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>218</v>
       </c>
@@ -5554,10 +5545,10 @@
         <v>202</v>
       </c>
       <c r="CA55" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="56" spans="1:79" x14ac:dyDescent="0.35">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="56" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>220</v>
       </c>
@@ -5568,10 +5559,10 @@
         <v>204</v>
       </c>
       <c r="CA56" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="57" spans="1:79" x14ac:dyDescent="0.35">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="57" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>222</v>
       </c>
@@ -5582,10 +5573,10 @@
         <v>206</v>
       </c>
       <c r="CA57" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="58" spans="1:79" x14ac:dyDescent="0.35">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="58" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>224</v>
       </c>
@@ -5596,10 +5587,10 @@
         <v>208</v>
       </c>
       <c r="CA58" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="59" spans="1:79" x14ac:dyDescent="0.35">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="59" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>226</v>
       </c>
@@ -5610,10 +5601,10 @@
         <v>210</v>
       </c>
       <c r="CA59" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="60" spans="1:79" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="60" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>228</v>
       </c>
@@ -5624,10 +5615,10 @@
         <v>212</v>
       </c>
       <c r="CA60" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="61" spans="1:79" x14ac:dyDescent="0.35">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="61" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>230</v>
       </c>
@@ -5638,10 +5629,10 @@
         <v>214</v>
       </c>
       <c r="CA61" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="62" spans="1:79" x14ac:dyDescent="0.35">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="62" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>347</v>
       </c>
@@ -5652,10 +5643,10 @@
         <v>216</v>
       </c>
       <c r="CA62" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="63" spans="1:79" x14ac:dyDescent="0.35">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="63" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>349</v>
       </c>
@@ -5666,10 +5657,10 @@
         <v>218</v>
       </c>
       <c r="CA63" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="64" spans="1:79" x14ac:dyDescent="0.35">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="64" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>350</v>
       </c>
@@ -5680,10 +5671,10 @@
         <v>220</v>
       </c>
       <c r="CA64" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="65" spans="1:79" x14ac:dyDescent="0.35">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="65" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>352</v>
       </c>
@@ -5694,10 +5685,10 @@
         <v>222</v>
       </c>
       <c r="CA65" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="66" spans="1:79" x14ac:dyDescent="0.35">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="66" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>354</v>
       </c>
@@ -5708,10 +5699,10 @@
         <v>224</v>
       </c>
       <c r="CA66" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="67" spans="1:79" x14ac:dyDescent="0.35">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="67" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>356</v>
       </c>
@@ -5722,10 +5713,10 @@
         <v>226</v>
       </c>
       <c r="CA67" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="68" spans="1:79" x14ac:dyDescent="0.35">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="68" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>358</v>
       </c>
@@ -5736,10 +5727,10 @@
         <v>228</v>
       </c>
       <c r="CA68" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="69" spans="1:79" x14ac:dyDescent="0.35">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="69" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>360</v>
       </c>
@@ -5750,10 +5741,10 @@
         <v>230</v>
       </c>
       <c r="CA69" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="70" spans="1:79" x14ac:dyDescent="0.35">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="70" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>362</v>
       </c>
@@ -5764,10 +5755,10 @@
         <v>347</v>
       </c>
       <c r="CA70" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="71" spans="1:79" x14ac:dyDescent="0.35">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="71" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>363</v>
       </c>
@@ -5778,10 +5769,10 @@
         <v>349</v>
       </c>
       <c r="CA71" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="72" spans="1:79" x14ac:dyDescent="0.35">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="72" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>364</v>
       </c>
@@ -5799,10 +5790,10 @@
         <v>350</v>
       </c>
       <c r="CA72" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="73" spans="1:79" x14ac:dyDescent="0.35">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="73" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>366</v>
       </c>
@@ -5813,10 +5804,10 @@
         <v>352</v>
       </c>
       <c r="CA73" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="74" spans="1:79" x14ac:dyDescent="0.35">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="74" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>368</v>
       </c>
@@ -5827,10 +5818,10 @@
         <v>354</v>
       </c>
       <c r="CA74" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="75" spans="1:79" x14ac:dyDescent="0.35">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="75" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>370</v>
       </c>
@@ -5841,10 +5832,10 @@
         <v>356</v>
       </c>
       <c r="CA75" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="76" spans="1:79" x14ac:dyDescent="0.35">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="76" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>372</v>
       </c>
@@ -5855,10 +5846,10 @@
         <v>358</v>
       </c>
       <c r="CA76" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="77" spans="1:79" x14ac:dyDescent="0.35">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="77" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>374</v>
       </c>
@@ -5869,10 +5860,10 @@
         <v>360</v>
       </c>
       <c r="CA77" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="78" spans="1:79" x14ac:dyDescent="0.35">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="78" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>376</v>
       </c>
@@ -5883,10 +5874,10 @@
         <v>362</v>
       </c>
       <c r="CA78" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="79" spans="1:79" x14ac:dyDescent="0.35">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="79" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>378</v>
       </c>
@@ -5897,10 +5888,10 @@
         <v>363</v>
       </c>
       <c r="CA79" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="80" spans="1:79" x14ac:dyDescent="0.35">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="80" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>18</v>
       </c>
@@ -5914,7 +5905,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="81" spans="1:146" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:146" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>20</v>
       </c>
@@ -5928,7 +5919,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="82" spans="1:146" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:146" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>22</v>
       </c>
@@ -5942,7 +5933,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="83" spans="1:146" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:146" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>24</v>
       </c>
@@ -5956,7 +5947,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="84" spans="1:146" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:146" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>26</v>
       </c>
@@ -5970,7 +5961,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="85" spans="1:146" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:146" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>27</v>
       </c>
@@ -5984,7 +5975,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="86" spans="1:146" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:146" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>28</v>
       </c>
@@ -5998,7 +5989,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="87" spans="1:146" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:146" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>29</v>
       </c>
@@ -6012,7 +6003,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="88" spans="1:146" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:146" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>31</v>
       </c>
@@ -6026,7 +6017,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="90" spans="1:146" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:146" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>30</v>
       </c>
@@ -6265,208 +6256,208 @@
         <v>33</v>
       </c>
       <c r="CB90" t="s">
-        <v>690</v>
+        <v>516</v>
       </c>
       <c r="CC90" t="s">
-        <v>691</v>
+        <v>517</v>
       </c>
       <c r="CD90" t="s">
-        <v>692</v>
+        <v>518</v>
       </c>
       <c r="CE90" t="s">
-        <v>693</v>
+        <v>519</v>
       </c>
       <c r="CF90" t="s">
-        <v>694</v>
+        <v>520</v>
       </c>
       <c r="CG90" t="s">
-        <v>695</v>
+        <v>521</v>
       </c>
       <c r="CH90" t="s">
-        <v>696</v>
+        <v>522</v>
       </c>
       <c r="CI90" t="s">
-        <v>697</v>
+        <v>523</v>
       </c>
       <c r="CJ90" t="s">
-        <v>698</v>
+        <v>524</v>
       </c>
       <c r="CK90" t="s">
-        <v>699</v>
+        <v>525</v>
       </c>
       <c r="CL90" t="s">
-        <v>700</v>
+        <v>526</v>
       </c>
       <c r="CM90" t="s">
-        <v>701</v>
+        <v>527</v>
       </c>
       <c r="CN90" t="s">
-        <v>702</v>
+        <v>528</v>
       </c>
       <c r="CO90" t="s">
-        <v>703</v>
+        <v>529</v>
       </c>
       <c r="CP90" t="s">
-        <v>704</v>
+        <v>530</v>
       </c>
       <c r="CQ90" t="s">
-        <v>705</v>
+        <v>531</v>
       </c>
       <c r="CR90" t="s">
-        <v>706</v>
+        <v>532</v>
       </c>
       <c r="CS90" t="s">
-        <v>707</v>
+        <v>533</v>
       </c>
       <c r="CT90" t="s">
-        <v>708</v>
+        <v>534</v>
       </c>
       <c r="CU90" t="s">
-        <v>709</v>
+        <v>535</v>
       </c>
       <c r="CV90" t="s">
-        <v>710</v>
+        <v>536</v>
       </c>
       <c r="CW90" t="s">
-        <v>711</v>
+        <v>537</v>
       </c>
       <c r="CX90" t="s">
-        <v>712</v>
+        <v>538</v>
       </c>
       <c r="CY90" t="s">
-        <v>713</v>
+        <v>539</v>
       </c>
       <c r="CZ90" t="s">
-        <v>714</v>
+        <v>540</v>
       </c>
       <c r="DA90" t="s">
-        <v>715</v>
+        <v>541</v>
       </c>
       <c r="DB90" t="s">
-        <v>716</v>
+        <v>542</v>
       </c>
       <c r="DC90" t="s">
-        <v>717</v>
+        <v>543</v>
       </c>
       <c r="DD90" t="s">
-        <v>718</v>
+        <v>544</v>
       </c>
       <c r="DE90" t="s">
-        <v>719</v>
+        <v>545</v>
       </c>
       <c r="DF90" t="s">
-        <v>720</v>
+        <v>546</v>
       </c>
       <c r="DG90" t="s">
-        <v>721</v>
+        <v>547</v>
       </c>
       <c r="DH90" t="s">
-        <v>722</v>
+        <v>548</v>
       </c>
       <c r="DI90" t="s">
-        <v>723</v>
+        <v>549</v>
       </c>
       <c r="DJ90" t="s">
-        <v>724</v>
+        <v>550</v>
       </c>
       <c r="DK90" t="s">
-        <v>725</v>
+        <v>551</v>
       </c>
       <c r="DL90" t="s">
-        <v>726</v>
+        <v>552</v>
       </c>
       <c r="DM90" t="s">
-        <v>727</v>
+        <v>553</v>
       </c>
       <c r="DN90" t="s">
-        <v>728</v>
+        <v>554</v>
       </c>
       <c r="DO90" t="s">
-        <v>729</v>
+        <v>555</v>
       </c>
       <c r="DP90" t="s">
-        <v>730</v>
+        <v>556</v>
       </c>
       <c r="DQ90" t="s">
-        <v>731</v>
+        <v>557</v>
       </c>
       <c r="DR90" t="s">
-        <v>732</v>
+        <v>558</v>
       </c>
       <c r="DS90" t="s">
-        <v>733</v>
+        <v>559</v>
       </c>
       <c r="DT90" t="s">
-        <v>734</v>
+        <v>560</v>
       </c>
       <c r="DU90" t="s">
-        <v>735</v>
+        <v>561</v>
       </c>
       <c r="DV90" t="s">
-        <v>736</v>
+        <v>562</v>
       </c>
       <c r="DW90" t="s">
-        <v>737</v>
+        <v>563</v>
       </c>
       <c r="DX90" t="s">
-        <v>738</v>
+        <v>564</v>
       </c>
       <c r="DY90" t="s">
-        <v>739</v>
+        <v>565</v>
       </c>
       <c r="DZ90" t="s">
-        <v>740</v>
+        <v>566</v>
       </c>
       <c r="EA90" t="s">
-        <v>741</v>
+        <v>567</v>
       </c>
       <c r="EB90" t="s">
-        <v>742</v>
+        <v>568</v>
       </c>
       <c r="EC90" t="s">
-        <v>743</v>
+        <v>569</v>
       </c>
       <c r="ED90" t="s">
-        <v>744</v>
+        <v>570</v>
       </c>
       <c r="EE90" t="s">
-        <v>745</v>
+        <v>571</v>
       </c>
       <c r="EF90" t="s">
-        <v>746</v>
+        <v>572</v>
       </c>
       <c r="EG90" t="s">
-        <v>747</v>
+        <v>573</v>
       </c>
       <c r="EH90" t="s">
-        <v>748</v>
+        <v>574</v>
       </c>
       <c r="EI90" t="s">
-        <v>749</v>
+        <v>575</v>
       </c>
       <c r="EJ90" t="s">
-        <v>750</v>
+        <v>576</v>
       </c>
       <c r="EK90" t="s">
-        <v>751</v>
+        <v>577</v>
       </c>
       <c r="EL90" t="s">
-        <v>752</v>
+        <v>578</v>
       </c>
       <c r="EM90" t="s">
-        <v>753</v>
+        <v>579</v>
       </c>
       <c r="EN90" t="s">
-        <v>754</v>
+        <v>580</v>
       </c>
       <c r="EO90" t="s">
-        <v>755</v>
+        <v>581</v>
       </c>
       <c r="EP90" t="s">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="91" spans="1:146" x14ac:dyDescent="0.35">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="91" spans="1:146" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>41</v>
       </c>
@@ -6474,229 +6465,229 @@
         <v>42</v>
       </c>
       <c r="C91" t="s">
+        <v>631</v>
+      </c>
+      <c r="D91" t="s">
         <v>398</v>
       </c>
-      <c r="D91" t="s">
+      <c r="E91" t="s">
         <v>399</v>
       </c>
-      <c r="E91" t="s">
+      <c r="F91" t="s">
+        <v>632</v>
+      </c>
+      <c r="G91" t="s">
+        <v>633</v>
+      </c>
+      <c r="H91" t="s">
         <v>400</v>
       </c>
-      <c r="F91" t="s">
+      <c r="I91" t="s">
         <v>401</v>
       </c>
-      <c r="G91" t="s">
+      <c r="J91" t="s">
+        <v>634</v>
+      </c>
+      <c r="K91" t="s">
+        <v>635</v>
+      </c>
+      <c r="L91" t="s">
+        <v>636</v>
+      </c>
+      <c r="M91" t="s">
+        <v>637</v>
+      </c>
+      <c r="N91" t="s">
         <v>402</v>
       </c>
-      <c r="H91" t="s">
+      <c r="O91" t="s">
+        <v>638</v>
+      </c>
+      <c r="P91" t="s">
+        <v>639</v>
+      </c>
+      <c r="Q91" t="s">
+        <v>640</v>
+      </c>
+      <c r="R91" t="s">
+        <v>641</v>
+      </c>
+      <c r="S91" t="s">
+        <v>642</v>
+      </c>
+      <c r="T91" t="s">
         <v>403</v>
       </c>
-      <c r="I91" t="s">
+      <c r="U91" t="s">
+        <v>643</v>
+      </c>
+      <c r="V91" t="s">
+        <v>644</v>
+      </c>
+      <c r="W91" t="s">
+        <v>645</v>
+      </c>
+      <c r="X91" t="s">
+        <v>646</v>
+      </c>
+      <c r="Y91" t="s">
         <v>404</v>
       </c>
-      <c r="J91" t="s">
+      <c r="Z91" t="s">
+        <v>647</v>
+      </c>
+      <c r="AA91" t="s">
         <v>405</v>
       </c>
-      <c r="K91" t="s">
+      <c r="AB91" t="s">
+        <v>648</v>
+      </c>
+      <c r="AC91" t="s">
+        <v>649</v>
+      </c>
+      <c r="AD91" t="s">
         <v>406</v>
       </c>
-      <c r="L91" t="s">
+      <c r="AE91" t="s">
         <v>407</v>
       </c>
-      <c r="M91" t="s">
+      <c r="AF91" t="s">
+        <v>650</v>
+      </c>
+      <c r="AG91" t="s">
+        <v>651</v>
+      </c>
+      <c r="AH91" t="s">
+        <v>652</v>
+      </c>
+      <c r="AI91" t="s">
+        <v>653</v>
+      </c>
+      <c r="AJ91" t="s">
+        <v>654</v>
+      </c>
+      <c r="AK91" t="s">
         <v>408</v>
       </c>
-      <c r="N91" t="s">
+      <c r="AL91" t="s">
+        <v>655</v>
+      </c>
+      <c r="AM91" t="s">
         <v>409</v>
       </c>
-      <c r="O91" t="s">
+      <c r="AN91" t="s">
+        <v>656</v>
+      </c>
+      <c r="AO91" t="s">
+        <v>657</v>
+      </c>
+      <c r="AP91" t="s">
+        <v>658</v>
+      </c>
+      <c r="AQ91" t="s">
+        <v>659</v>
+      </c>
+      <c r="AR91" t="s">
         <v>410</v>
       </c>
-      <c r="P91" t="s">
+      <c r="AS91" t="s">
+        <v>660</v>
+      </c>
+      <c r="AT91" t="s">
+        <v>661</v>
+      </c>
+      <c r="AU91" t="s">
+        <v>662</v>
+      </c>
+      <c r="AV91" t="s">
         <v>411</v>
       </c>
-      <c r="Q91" t="s">
+      <c r="AW91" t="s">
+        <v>663</v>
+      </c>
+      <c r="AX91" t="s">
+        <v>664</v>
+      </c>
+      <c r="AY91" t="s">
+        <v>665</v>
+      </c>
+      <c r="AZ91" t="s">
+        <v>666</v>
+      </c>
+      <c r="BA91" t="s">
+        <v>667</v>
+      </c>
+      <c r="BB91" t="s">
+        <v>668</v>
+      </c>
+      <c r="BC91" t="s">
+        <v>669</v>
+      </c>
+      <c r="BD91" t="s">
+        <v>670</v>
+      </c>
+      <c r="BE91" t="s">
+        <v>671</v>
+      </c>
+      <c r="BF91" t="s">
+        <v>672</v>
+      </c>
+      <c r="BG91" t="s">
+        <v>673</v>
+      </c>
+      <c r="BH91" t="s">
         <v>412</v>
       </c>
-      <c r="R91" t="s">
+      <c r="BI91" t="s">
+        <v>674</v>
+      </c>
+      <c r="BJ91" t="s">
+        <v>675</v>
+      </c>
+      <c r="BK91" t="s">
+        <v>676</v>
+      </c>
+      <c r="BL91" t="s">
+        <v>677</v>
+      </c>
+      <c r="BM91" t="s">
+        <v>678</v>
+      </c>
+      <c r="BN91" t="s">
         <v>413</v>
       </c>
-      <c r="S91" t="s">
+      <c r="BO91" t="s">
+        <v>679</v>
+      </c>
+      <c r="BP91" t="s">
+        <v>680</v>
+      </c>
+      <c r="BQ91" t="s">
+        <v>681</v>
+      </c>
+      <c r="BR91" t="s">
+        <v>682</v>
+      </c>
+      <c r="BS91" t="s">
+        <v>683</v>
+      </c>
+      <c r="BT91" t="s">
+        <v>684</v>
+      </c>
+      <c r="BU91" t="s">
+        <v>685</v>
+      </c>
+      <c r="BV91" t="s">
+        <v>686</v>
+      </c>
+      <c r="BW91" t="s">
+        <v>687</v>
+      </c>
+      <c r="BX91" t="s">
         <v>414</v>
       </c>
-      <c r="T91" t="s">
-        <v>415</v>
-      </c>
-      <c r="U91" t="s">
-        <v>416</v>
-      </c>
-      <c r="V91" t="s">
-        <v>417</v>
-      </c>
-      <c r="W91" t="s">
-        <v>418</v>
-      </c>
-      <c r="X91" t="s">
-        <v>419</v>
-      </c>
-      <c r="Y91" t="s">
-        <v>420</v>
-      </c>
-      <c r="Z91" t="s">
-        <v>421</v>
-      </c>
-      <c r="AA91" t="s">
-        <v>422</v>
-      </c>
-      <c r="AB91" t="s">
-        <v>423</v>
-      </c>
-      <c r="AC91" t="s">
-        <v>424</v>
-      </c>
-      <c r="AD91" t="s">
-        <v>425</v>
-      </c>
-      <c r="AE91" t="s">
-        <v>426</v>
-      </c>
-      <c r="AF91" t="s">
-        <v>427</v>
-      </c>
-      <c r="AG91" t="s">
-        <v>428</v>
-      </c>
-      <c r="AH91" t="s">
-        <v>429</v>
-      </c>
-      <c r="AI91" t="s">
-        <v>430</v>
-      </c>
-      <c r="AJ91" t="s">
-        <v>431</v>
-      </c>
-      <c r="AK91" t="s">
-        <v>432</v>
-      </c>
-      <c r="AL91" t="s">
-        <v>433</v>
-      </c>
-      <c r="AM91" t="s">
-        <v>434</v>
-      </c>
-      <c r="AN91" t="s">
-        <v>435</v>
-      </c>
-      <c r="AO91" t="s">
-        <v>436</v>
-      </c>
-      <c r="AP91" t="s">
-        <v>437</v>
-      </c>
-      <c r="AQ91" t="s">
-        <v>438</v>
-      </c>
-      <c r="AR91" t="s">
-        <v>439</v>
-      </c>
-      <c r="AS91" t="s">
-        <v>440</v>
-      </c>
-      <c r="AT91" t="s">
-        <v>441</v>
-      </c>
-      <c r="AU91" t="s">
-        <v>442</v>
-      </c>
-      <c r="AV91" t="s">
-        <v>443</v>
-      </c>
-      <c r="AW91" t="s">
-        <v>444</v>
-      </c>
-      <c r="AX91" t="s">
-        <v>445</v>
-      </c>
-      <c r="AY91" t="s">
-        <v>446</v>
-      </c>
-      <c r="AZ91" t="s">
-        <v>447</v>
-      </c>
-      <c r="BA91" t="s">
-        <v>448</v>
-      </c>
-      <c r="BB91" t="s">
-        <v>449</v>
-      </c>
-      <c r="BC91" t="s">
-        <v>450</v>
-      </c>
-      <c r="BD91" t="s">
-        <v>451</v>
-      </c>
-      <c r="BE91" t="s">
-        <v>452</v>
-      </c>
-      <c r="BF91" t="s">
-        <v>453</v>
-      </c>
-      <c r="BG91" t="s">
-        <v>454</v>
-      </c>
-      <c r="BH91" t="s">
-        <v>455</v>
-      </c>
-      <c r="BI91" t="s">
-        <v>456</v>
-      </c>
-      <c r="BJ91" t="s">
-        <v>457</v>
-      </c>
-      <c r="BK91" t="s">
-        <v>458</v>
-      </c>
-      <c r="BL91" t="s">
-        <v>459</v>
-      </c>
-      <c r="BM91" t="s">
-        <v>460</v>
-      </c>
-      <c r="BN91" t="s">
-        <v>461</v>
-      </c>
-      <c r="BO91" t="s">
-        <v>462</v>
-      </c>
-      <c r="BP91" t="s">
-        <v>463</v>
-      </c>
-      <c r="BQ91" t="s">
-        <v>464</v>
-      </c>
-      <c r="BR91" t="s">
-        <v>465</v>
-      </c>
-      <c r="BS91" t="s">
-        <v>466</v>
-      </c>
-      <c r="BT91" t="s">
-        <v>467</v>
-      </c>
-      <c r="BU91" t="s">
-        <v>468</v>
-      </c>
-      <c r="BV91" t="s">
-        <v>469</v>
-      </c>
-      <c r="BW91" t="s">
-        <v>470</v>
-      </c>
-      <c r="BX91" t="s">
-        <v>471</v>
-      </c>
       <c r="BY91" t="s">
-        <v>472</v>
+        <v>688</v>
       </c>
       <c r="BZ91" t="s">
         <v>41</v>
@@ -6705,208 +6696,208 @@
         <v>42</v>
       </c>
       <c r="CB91" t="s">
-        <v>757</v>
+        <v>805</v>
       </c>
       <c r="CC91" t="s">
-        <v>758</v>
+        <v>806</v>
       </c>
       <c r="CD91" t="s">
-        <v>759</v>
+        <v>807</v>
       </c>
       <c r="CE91" t="s">
-        <v>760</v>
+        <v>583</v>
       </c>
       <c r="CF91" t="s">
-        <v>761</v>
+        <v>584</v>
       </c>
       <c r="CG91" t="s">
-        <v>762</v>
+        <v>585</v>
       </c>
       <c r="CH91" t="s">
-        <v>763</v>
+        <v>808</v>
       </c>
       <c r="CI91" t="s">
-        <v>764</v>
+        <v>809</v>
       </c>
       <c r="CJ91" t="s">
-        <v>765</v>
+        <v>586</v>
       </c>
       <c r="CK91" t="s">
-        <v>766</v>
+        <v>810</v>
       </c>
       <c r="CL91" t="s">
-        <v>767</v>
+        <v>811</v>
       </c>
       <c r="CM91" t="s">
-        <v>768</v>
+        <v>812</v>
       </c>
       <c r="CN91" t="s">
-        <v>769</v>
+        <v>813</v>
       </c>
       <c r="CO91" t="s">
-        <v>770</v>
+        <v>814</v>
       </c>
       <c r="CP91" t="s">
-        <v>771</v>
+        <v>815</v>
       </c>
       <c r="CQ91" t="s">
-        <v>772</v>
+        <v>816</v>
       </c>
       <c r="CR91" t="s">
-        <v>773</v>
+        <v>587</v>
       </c>
       <c r="CS91" t="s">
-        <v>774</v>
+        <v>817</v>
       </c>
       <c r="CT91" t="s">
-        <v>775</v>
+        <v>818</v>
       </c>
       <c r="CU91" t="s">
-        <v>776</v>
+        <v>819</v>
       </c>
       <c r="CV91" t="s">
-        <v>777</v>
+        <v>820</v>
       </c>
       <c r="CW91" t="s">
-        <v>778</v>
+        <v>821</v>
       </c>
       <c r="CX91" t="s">
-        <v>779</v>
+        <v>588</v>
       </c>
       <c r="CY91" t="s">
-        <v>780</v>
+        <v>589</v>
       </c>
       <c r="CZ91" t="s">
-        <v>781</v>
+        <v>822</v>
       </c>
       <c r="DA91" t="s">
-        <v>782</v>
+        <v>823</v>
       </c>
       <c r="DB91" t="s">
-        <v>783</v>
+        <v>824</v>
       </c>
       <c r="DC91" t="s">
-        <v>784</v>
+        <v>825</v>
       </c>
       <c r="DD91" t="s">
-        <v>785</v>
+        <v>826</v>
       </c>
       <c r="DE91" t="s">
-        <v>786</v>
+        <v>827</v>
       </c>
       <c r="DF91" t="s">
-        <v>787</v>
+        <v>590</v>
       </c>
       <c r="DG91" t="s">
-        <v>788</v>
+        <v>591</v>
       </c>
       <c r="DH91" t="s">
-        <v>789</v>
+        <v>828</v>
       </c>
       <c r="DI91" t="s">
-        <v>790</v>
+        <v>829</v>
       </c>
       <c r="DJ91" t="s">
-        <v>791</v>
+        <v>830</v>
       </c>
       <c r="DK91" t="s">
-        <v>792</v>
+        <v>831</v>
       </c>
       <c r="DL91" t="s">
-        <v>793</v>
+        <v>832</v>
       </c>
       <c r="DM91" t="s">
-        <v>794</v>
+        <v>833</v>
       </c>
       <c r="DN91" t="s">
-        <v>795</v>
+        <v>834</v>
       </c>
       <c r="DO91" t="s">
-        <v>796</v>
+        <v>835</v>
       </c>
       <c r="DP91" t="s">
-        <v>797</v>
+        <v>592</v>
       </c>
       <c r="DQ91" t="s">
-        <v>798</v>
+        <v>836</v>
       </c>
       <c r="DR91" t="s">
-        <v>799</v>
+        <v>837</v>
       </c>
       <c r="DS91" t="s">
-        <v>800</v>
+        <v>838</v>
       </c>
       <c r="DT91" t="s">
-        <v>801</v>
+        <v>839</v>
       </c>
       <c r="DU91" t="s">
-        <v>802</v>
+        <v>593</v>
       </c>
       <c r="DV91" t="s">
-        <v>803</v>
+        <v>594</v>
       </c>
       <c r="DW91" t="s">
-        <v>804</v>
+        <v>840</v>
       </c>
       <c r="DX91" t="s">
-        <v>805</v>
+        <v>398</v>
       </c>
       <c r="DY91" t="s">
-        <v>806</v>
+        <v>841</v>
       </c>
       <c r="DZ91" t="s">
-        <v>807</v>
+        <v>842</v>
       </c>
       <c r="EA91" t="s">
-        <v>808</v>
+        <v>595</v>
       </c>
       <c r="EB91" t="s">
-        <v>809</v>
+        <v>843</v>
       </c>
       <c r="EC91" t="s">
-        <v>810</v>
+        <v>844</v>
       </c>
       <c r="ED91" t="s">
-        <v>811</v>
+        <v>596</v>
       </c>
       <c r="EE91" t="s">
-        <v>812</v>
+        <v>845</v>
       </c>
       <c r="EF91" t="s">
-        <v>813</v>
+        <v>597</v>
       </c>
       <c r="EG91" t="s">
-        <v>814</v>
+        <v>846</v>
       </c>
       <c r="EH91" t="s">
-        <v>815</v>
+        <v>847</v>
       </c>
       <c r="EI91" t="s">
-        <v>816</v>
+        <v>598</v>
       </c>
       <c r="EJ91" t="s">
-        <v>817</v>
+        <v>848</v>
       </c>
       <c r="EK91" t="s">
-        <v>818</v>
+        <v>849</v>
       </c>
       <c r="EL91" t="s">
-        <v>819</v>
+        <v>850</v>
       </c>
       <c r="EM91" t="s">
-        <v>820</v>
+        <v>851</v>
       </c>
       <c r="EN91" t="s">
-        <v>821</v>
+        <v>852</v>
       </c>
       <c r="EO91" t="s">
-        <v>822</v>
+        <v>853</v>
       </c>
       <c r="EP91" t="s">
-        <v>823</v>
-      </c>
-    </row>
-    <row r="92" spans="1:146" x14ac:dyDescent="0.35">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="92" spans="1:146" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>43</v>
       </c>
@@ -6914,229 +6905,229 @@
         <v>42</v>
       </c>
       <c r="C92" t="s">
-        <v>473</v>
+        <v>689</v>
       </c>
       <c r="D92" t="s">
-        <v>474</v>
+        <v>415</v>
       </c>
       <c r="E92" t="s">
-        <v>475</v>
+        <v>416</v>
       </c>
       <c r="F92" t="s">
-        <v>476</v>
+        <v>690</v>
       </c>
       <c r="G92" t="s">
-        <v>477</v>
+        <v>691</v>
       </c>
       <c r="H92" t="s">
-        <v>478</v>
+        <v>417</v>
       </c>
       <c r="I92" t="s">
-        <v>479</v>
+        <v>418</v>
       </c>
       <c r="J92" t="s">
-        <v>480</v>
+        <v>692</v>
       </c>
       <c r="K92" t="s">
-        <v>481</v>
+        <v>693</v>
       </c>
       <c r="L92" t="s">
-        <v>482</v>
+        <v>694</v>
       </c>
       <c r="M92" t="s">
-        <v>483</v>
+        <v>695</v>
       </c>
       <c r="N92" t="s">
-        <v>484</v>
+        <v>419</v>
       </c>
       <c r="O92" t="s">
-        <v>485</v>
+        <v>696</v>
       </c>
       <c r="P92" t="s">
-        <v>486</v>
+        <v>697</v>
       </c>
       <c r="Q92" t="s">
-        <v>487</v>
+        <v>698</v>
       </c>
       <c r="R92" t="s">
-        <v>488</v>
+        <v>699</v>
       </c>
       <c r="S92" t="s">
-        <v>489</v>
+        <v>700</v>
       </c>
       <c r="T92" t="s">
-        <v>490</v>
+        <v>420</v>
       </c>
       <c r="U92" t="s">
-        <v>491</v>
+        <v>701</v>
       </c>
       <c r="V92" t="s">
-        <v>492</v>
+        <v>702</v>
       </c>
       <c r="W92" t="s">
-        <v>493</v>
+        <v>703</v>
       </c>
       <c r="X92" t="s">
-        <v>494</v>
+        <v>704</v>
       </c>
       <c r="Y92" t="s">
-        <v>495</v>
+        <v>421</v>
       </c>
       <c r="Z92" t="s">
-        <v>496</v>
+        <v>705</v>
       </c>
       <c r="AA92" t="s">
-        <v>497</v>
+        <v>422</v>
       </c>
       <c r="AB92" t="s">
-        <v>498</v>
+        <v>706</v>
       </c>
       <c r="AC92" t="s">
-        <v>499</v>
+        <v>707</v>
       </c>
       <c r="AD92" t="s">
-        <v>500</v>
+        <v>423</v>
       </c>
       <c r="AE92" t="s">
-        <v>501</v>
+        <v>424</v>
       </c>
       <c r="AF92" t="s">
-        <v>502</v>
+        <v>708</v>
       </c>
       <c r="AG92" t="s">
-        <v>503</v>
+        <v>709</v>
       </c>
       <c r="AH92" t="s">
-        <v>504</v>
+        <v>710</v>
       </c>
       <c r="AI92" t="s">
-        <v>505</v>
+        <v>711</v>
       </c>
       <c r="AJ92" t="s">
-        <v>506</v>
+        <v>712</v>
       </c>
       <c r="AK92" t="s">
-        <v>507</v>
+        <v>425</v>
       </c>
       <c r="AL92" t="s">
-        <v>508</v>
+        <v>713</v>
       </c>
       <c r="AM92" t="s">
-        <v>509</v>
+        <v>426</v>
       </c>
       <c r="AN92" t="s">
-        <v>510</v>
+        <v>714</v>
       </c>
       <c r="AO92" t="s">
-        <v>511</v>
+        <v>715</v>
       </c>
       <c r="AP92" t="s">
-        <v>512</v>
+        <v>716</v>
       </c>
       <c r="AQ92" t="s">
-        <v>513</v>
+        <v>717</v>
       </c>
       <c r="AR92" t="s">
-        <v>514</v>
+        <v>427</v>
       </c>
       <c r="AS92" t="s">
-        <v>515</v>
+        <v>718</v>
       </c>
       <c r="AT92" t="s">
-        <v>516</v>
+        <v>719</v>
       </c>
       <c r="AU92" t="s">
-        <v>517</v>
+        <v>720</v>
       </c>
       <c r="AV92" t="s">
-        <v>518</v>
+        <v>428</v>
       </c>
       <c r="AW92" t="s">
-        <v>519</v>
+        <v>721</v>
       </c>
       <c r="AX92" t="s">
-        <v>520</v>
+        <v>722</v>
       </c>
       <c r="AY92" t="s">
-        <v>521</v>
+        <v>723</v>
       </c>
       <c r="AZ92" t="s">
-        <v>522</v>
+        <v>724</v>
       </c>
       <c r="BA92" t="s">
-        <v>523</v>
+        <v>725</v>
       </c>
       <c r="BB92" t="s">
-        <v>524</v>
+        <v>726</v>
       </c>
       <c r="BC92" t="s">
-        <v>525</v>
+        <v>727</v>
       </c>
       <c r="BD92" t="s">
-        <v>526</v>
+        <v>728</v>
       </c>
       <c r="BE92" t="s">
-        <v>527</v>
+        <v>729</v>
       </c>
       <c r="BF92" t="s">
-        <v>528</v>
+        <v>730</v>
       </c>
       <c r="BG92" t="s">
-        <v>529</v>
+        <v>731</v>
       </c>
       <c r="BH92" t="s">
-        <v>530</v>
+        <v>429</v>
       </c>
       <c r="BI92" t="s">
-        <v>531</v>
+        <v>732</v>
       </c>
       <c r="BJ92" t="s">
-        <v>532</v>
+        <v>733</v>
       </c>
       <c r="BK92" t="s">
-        <v>533</v>
+        <v>734</v>
       </c>
       <c r="BL92" t="s">
-        <v>534</v>
+        <v>735</v>
       </c>
       <c r="BM92" t="s">
-        <v>535</v>
+        <v>736</v>
       </c>
       <c r="BN92" t="s">
-        <v>536</v>
+        <v>430</v>
       </c>
       <c r="BO92" t="s">
-        <v>537</v>
+        <v>737</v>
       </c>
       <c r="BP92" t="s">
-        <v>538</v>
+        <v>738</v>
       </c>
       <c r="BQ92" t="s">
-        <v>539</v>
+        <v>739</v>
       </c>
       <c r="BR92" t="s">
-        <v>540</v>
+        <v>740</v>
       </c>
       <c r="BS92" t="s">
-        <v>541</v>
+        <v>741</v>
       </c>
       <c r="BT92" t="s">
-        <v>542</v>
+        <v>742</v>
       </c>
       <c r="BU92" t="s">
-        <v>543</v>
+        <v>743</v>
       </c>
       <c r="BV92" t="s">
-        <v>544</v>
+        <v>744</v>
       </c>
       <c r="BW92" t="s">
-        <v>545</v>
+        <v>745</v>
       </c>
       <c r="BX92" t="s">
-        <v>546</v>
+        <v>431</v>
       </c>
       <c r="BY92" t="s">
-        <v>547</v>
+        <v>746</v>
       </c>
       <c r="BZ92" t="s">
         <v>43</v>
@@ -7145,208 +7136,208 @@
         <v>42</v>
       </c>
       <c r="CB92" t="s">
-        <v>824</v>
+        <v>855</v>
       </c>
       <c r="CC92" t="s">
-        <v>825</v>
+        <v>856</v>
       </c>
       <c r="CD92" t="s">
-        <v>826</v>
+        <v>857</v>
       </c>
       <c r="CE92" t="s">
-        <v>827</v>
+        <v>599</v>
       </c>
       <c r="CF92" t="s">
-        <v>828</v>
+        <v>600</v>
       </c>
       <c r="CG92" t="s">
-        <v>829</v>
+        <v>601</v>
       </c>
       <c r="CH92" t="s">
-        <v>830</v>
+        <v>858</v>
       </c>
       <c r="CI92" t="s">
-        <v>831</v>
+        <v>859</v>
       </c>
       <c r="CJ92" t="s">
-        <v>832</v>
+        <v>602</v>
       </c>
       <c r="CK92" t="s">
-        <v>833</v>
+        <v>860</v>
       </c>
       <c r="CL92" t="s">
-        <v>834</v>
+        <v>861</v>
       </c>
       <c r="CM92" t="s">
-        <v>835</v>
+        <v>862</v>
       </c>
       <c r="CN92" t="s">
-        <v>836</v>
+        <v>863</v>
       </c>
       <c r="CO92" t="s">
-        <v>837</v>
+        <v>864</v>
       </c>
       <c r="CP92" t="s">
-        <v>838</v>
+        <v>865</v>
       </c>
       <c r="CQ92" t="s">
-        <v>839</v>
+        <v>866</v>
       </c>
       <c r="CR92" t="s">
-        <v>840</v>
+        <v>603</v>
       </c>
       <c r="CS92" t="s">
-        <v>841</v>
+        <v>867</v>
       </c>
       <c r="CT92" t="s">
-        <v>842</v>
+        <v>868</v>
       </c>
       <c r="CU92" t="s">
-        <v>843</v>
+        <v>869</v>
       </c>
       <c r="CV92" t="s">
-        <v>844</v>
+        <v>870</v>
       </c>
       <c r="CW92" t="s">
-        <v>845</v>
+        <v>871</v>
       </c>
       <c r="CX92" t="s">
-        <v>846</v>
+        <v>604</v>
       </c>
       <c r="CY92" t="s">
-        <v>847</v>
+        <v>605</v>
       </c>
       <c r="CZ92" t="s">
-        <v>848</v>
+        <v>872</v>
       </c>
       <c r="DA92" t="s">
-        <v>849</v>
+        <v>873</v>
       </c>
       <c r="DB92" t="s">
-        <v>850</v>
+        <v>874</v>
       </c>
       <c r="DC92" t="s">
-        <v>851</v>
+        <v>875</v>
       </c>
       <c r="DD92" t="s">
-        <v>852</v>
+        <v>876</v>
       </c>
       <c r="DE92" t="s">
-        <v>853</v>
+        <v>877</v>
       </c>
       <c r="DF92" t="s">
-        <v>854</v>
+        <v>606</v>
       </c>
       <c r="DG92" t="s">
-        <v>855</v>
+        <v>607</v>
       </c>
       <c r="DH92" t="s">
-        <v>856</v>
+        <v>878</v>
       </c>
       <c r="DI92" t="s">
-        <v>857</v>
+        <v>879</v>
       </c>
       <c r="DJ92" t="s">
-        <v>858</v>
+        <v>880</v>
       </c>
       <c r="DK92" t="s">
-        <v>859</v>
+        <v>881</v>
       </c>
       <c r="DL92" t="s">
-        <v>860</v>
+        <v>882</v>
       </c>
       <c r="DM92" t="s">
-        <v>861</v>
+        <v>883</v>
       </c>
       <c r="DN92" t="s">
-        <v>862</v>
+        <v>884</v>
       </c>
       <c r="DO92" t="s">
-        <v>863</v>
+        <v>885</v>
       </c>
       <c r="DP92" t="s">
-        <v>864</v>
+        <v>608</v>
       </c>
       <c r="DQ92" t="s">
-        <v>865</v>
+        <v>886</v>
       </c>
       <c r="DR92" t="s">
-        <v>866</v>
+        <v>887</v>
       </c>
       <c r="DS92" t="s">
-        <v>867</v>
+        <v>888</v>
       </c>
       <c r="DT92" t="s">
-        <v>868</v>
+        <v>889</v>
       </c>
       <c r="DU92" t="s">
-        <v>869</v>
+        <v>609</v>
       </c>
       <c r="DV92" t="s">
-        <v>870</v>
+        <v>610</v>
       </c>
       <c r="DW92" t="s">
-        <v>871</v>
+        <v>890</v>
       </c>
       <c r="DX92" t="s">
-        <v>872</v>
+        <v>415</v>
       </c>
       <c r="DY92" t="s">
-        <v>873</v>
+        <v>891</v>
       </c>
       <c r="DZ92" t="s">
-        <v>874</v>
+        <v>892</v>
       </c>
       <c r="EA92" t="s">
-        <v>875</v>
+        <v>611</v>
       </c>
       <c r="EB92" t="s">
-        <v>876</v>
+        <v>893</v>
       </c>
       <c r="EC92" t="s">
-        <v>877</v>
+        <v>894</v>
       </c>
       <c r="ED92" t="s">
-        <v>878</v>
+        <v>612</v>
       </c>
       <c r="EE92" t="s">
-        <v>879</v>
+        <v>895</v>
       </c>
       <c r="EF92" t="s">
-        <v>880</v>
+        <v>613</v>
       </c>
       <c r="EG92" t="s">
-        <v>881</v>
+        <v>896</v>
       </c>
       <c r="EH92" t="s">
-        <v>882</v>
+        <v>897</v>
       </c>
       <c r="EI92" t="s">
-        <v>883</v>
+        <v>614</v>
       </c>
       <c r="EJ92" t="s">
-        <v>884</v>
+        <v>898</v>
       </c>
       <c r="EK92" t="s">
-        <v>885</v>
+        <v>899</v>
       </c>
       <c r="EL92" t="s">
-        <v>886</v>
+        <v>900</v>
       </c>
       <c r="EM92" t="s">
-        <v>887</v>
+        <v>901</v>
       </c>
       <c r="EN92" t="s">
-        <v>888</v>
+        <v>902</v>
       </c>
       <c r="EO92" t="s">
-        <v>889</v>
+        <v>903</v>
       </c>
       <c r="EP92" t="s">
-        <v>890</v>
-      </c>
-    </row>
-    <row r="93" spans="1:146" x14ac:dyDescent="0.35">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="93" spans="1:146" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>44</v>
       </c>
@@ -7354,229 +7345,229 @@
         <v>42</v>
       </c>
       <c r="C93" t="s">
-        <v>548</v>
+        <v>747</v>
       </c>
       <c r="D93" t="s">
-        <v>549</v>
+        <v>432</v>
       </c>
       <c r="E93" t="s">
-        <v>550</v>
+        <v>433</v>
       </c>
       <c r="F93" t="s">
-        <v>551</v>
+        <v>748</v>
       </c>
       <c r="G93" t="s">
-        <v>552</v>
+        <v>749</v>
       </c>
       <c r="H93" t="s">
-        <v>553</v>
+        <v>434</v>
       </c>
       <c r="I93" t="s">
-        <v>554</v>
+        <v>435</v>
       </c>
       <c r="J93" t="s">
-        <v>555</v>
+        <v>750</v>
       </c>
       <c r="K93" t="s">
-        <v>556</v>
+        <v>751</v>
       </c>
       <c r="L93" t="s">
-        <v>557</v>
+        <v>752</v>
       </c>
       <c r="M93" t="s">
-        <v>558</v>
+        <v>753</v>
       </c>
       <c r="N93" t="s">
-        <v>559</v>
+        <v>436</v>
       </c>
       <c r="O93" t="s">
-        <v>560</v>
+        <v>754</v>
       </c>
       <c r="P93" t="s">
-        <v>561</v>
+        <v>755</v>
       </c>
       <c r="Q93" t="s">
-        <v>562</v>
+        <v>756</v>
       </c>
       <c r="R93" t="s">
-        <v>563</v>
+        <v>757</v>
       </c>
       <c r="S93" t="s">
-        <v>564</v>
+        <v>758</v>
       </c>
       <c r="T93" t="s">
-        <v>565</v>
+        <v>437</v>
       </c>
       <c r="U93" t="s">
-        <v>566</v>
+        <v>759</v>
       </c>
       <c r="V93" t="s">
-        <v>567</v>
+        <v>760</v>
       </c>
       <c r="W93" t="s">
-        <v>568</v>
+        <v>761</v>
       </c>
       <c r="X93" t="s">
-        <v>569</v>
+        <v>762</v>
       </c>
       <c r="Y93" t="s">
-        <v>570</v>
+        <v>438</v>
       </c>
       <c r="Z93" t="s">
-        <v>571</v>
+        <v>763</v>
       </c>
       <c r="AA93" t="s">
-        <v>572</v>
+        <v>439</v>
       </c>
       <c r="AB93" t="s">
-        <v>573</v>
+        <v>764</v>
       </c>
       <c r="AC93" t="s">
-        <v>574</v>
+        <v>765</v>
       </c>
       <c r="AD93" t="s">
-        <v>575</v>
+        <v>440</v>
       </c>
       <c r="AE93" t="s">
-        <v>576</v>
+        <v>441</v>
       </c>
       <c r="AF93" t="s">
-        <v>577</v>
+        <v>766</v>
       </c>
       <c r="AG93" t="s">
-        <v>578</v>
+        <v>767</v>
       </c>
       <c r="AH93" t="s">
-        <v>579</v>
+        <v>768</v>
       </c>
       <c r="AI93" t="s">
-        <v>580</v>
+        <v>769</v>
       </c>
       <c r="AJ93" t="s">
-        <v>581</v>
+        <v>770</v>
       </c>
       <c r="AK93" t="s">
-        <v>582</v>
+        <v>442</v>
       </c>
       <c r="AL93" t="s">
-        <v>583</v>
+        <v>771</v>
       </c>
       <c r="AM93" t="s">
-        <v>584</v>
+        <v>443</v>
       </c>
       <c r="AN93" t="s">
-        <v>585</v>
+        <v>772</v>
       </c>
       <c r="AO93" t="s">
-        <v>586</v>
+        <v>773</v>
       </c>
       <c r="AP93" t="s">
-        <v>587</v>
+        <v>774</v>
       </c>
       <c r="AQ93" t="s">
-        <v>588</v>
+        <v>775</v>
       </c>
       <c r="AR93" t="s">
-        <v>589</v>
+        <v>444</v>
       </c>
       <c r="AS93" t="s">
-        <v>590</v>
+        <v>776</v>
       </c>
       <c r="AT93" t="s">
-        <v>591</v>
+        <v>777</v>
       </c>
       <c r="AU93" t="s">
-        <v>592</v>
+        <v>778</v>
       </c>
       <c r="AV93" t="s">
-        <v>593</v>
+        <v>445</v>
       </c>
       <c r="AW93" t="s">
-        <v>594</v>
+        <v>779</v>
       </c>
       <c r="AX93" t="s">
-        <v>595</v>
+        <v>780</v>
       </c>
       <c r="AY93" t="s">
-        <v>596</v>
+        <v>781</v>
       </c>
       <c r="AZ93" t="s">
-        <v>597</v>
+        <v>782</v>
       </c>
       <c r="BA93" t="s">
-        <v>598</v>
+        <v>783</v>
       </c>
       <c r="BB93" t="s">
-        <v>599</v>
+        <v>784</v>
       </c>
       <c r="BC93" t="s">
-        <v>600</v>
+        <v>785</v>
       </c>
       <c r="BD93" t="s">
-        <v>601</v>
+        <v>786</v>
       </c>
       <c r="BE93" t="s">
-        <v>602</v>
+        <v>787</v>
       </c>
       <c r="BF93" t="s">
-        <v>603</v>
+        <v>788</v>
       </c>
       <c r="BG93" t="s">
-        <v>604</v>
+        <v>789</v>
       </c>
       <c r="BH93" t="s">
-        <v>605</v>
+        <v>446</v>
       </c>
       <c r="BI93" t="s">
-        <v>606</v>
+        <v>790</v>
       </c>
       <c r="BJ93" t="s">
-        <v>607</v>
+        <v>791</v>
       </c>
       <c r="BK93" t="s">
-        <v>608</v>
+        <v>792</v>
       </c>
       <c r="BL93" t="s">
-        <v>609</v>
+        <v>793</v>
       </c>
       <c r="BM93" t="s">
-        <v>610</v>
+        <v>794</v>
       </c>
       <c r="BN93" t="s">
-        <v>611</v>
+        <v>447</v>
       </c>
       <c r="BO93" t="s">
-        <v>612</v>
+        <v>795</v>
       </c>
       <c r="BP93" t="s">
-        <v>613</v>
+        <v>796</v>
       </c>
       <c r="BQ93" t="s">
-        <v>614</v>
+        <v>797</v>
       </c>
       <c r="BR93" t="s">
-        <v>615</v>
+        <v>798</v>
       </c>
       <c r="BS93" t="s">
-        <v>616</v>
+        <v>799</v>
       </c>
       <c r="BT93" t="s">
-        <v>617</v>
+        <v>800</v>
       </c>
       <c r="BU93" t="s">
-        <v>618</v>
+        <v>801</v>
       </c>
       <c r="BV93" t="s">
-        <v>619</v>
+        <v>802</v>
       </c>
       <c r="BW93" t="s">
-        <v>620</v>
+        <v>803</v>
       </c>
       <c r="BX93" t="s">
-        <v>621</v>
+        <v>448</v>
       </c>
       <c r="BY93" t="s">
-        <v>622</v>
+        <v>804</v>
       </c>
       <c r="BZ93" t="s">
         <v>44</v>
@@ -7585,160 +7576,160 @@
         <v>42</v>
       </c>
       <c r="CB93" t="s">
-        <v>891</v>
+        <v>905</v>
       </c>
       <c r="CC93" t="s">
-        <v>892</v>
+        <v>906</v>
       </c>
       <c r="CD93" t="s">
-        <v>893</v>
+        <v>907</v>
       </c>
       <c r="CE93" t="s">
-        <v>894</v>
+        <v>615</v>
       </c>
       <c r="CF93" t="s">
-        <v>895</v>
+        <v>616</v>
       </c>
       <c r="CG93" t="s">
-        <v>896</v>
+        <v>617</v>
       </c>
       <c r="CH93" t="s">
-        <v>897</v>
+        <v>908</v>
       </c>
       <c r="CI93" t="s">
-        <v>898</v>
+        <v>909</v>
       </c>
       <c r="CJ93" t="s">
-        <v>899</v>
+        <v>618</v>
       </c>
       <c r="CK93" t="s">
-        <v>900</v>
+        <v>910</v>
       </c>
       <c r="CL93" t="s">
-        <v>901</v>
+        <v>911</v>
       </c>
       <c r="CM93" t="s">
-        <v>902</v>
+        <v>912</v>
       </c>
       <c r="CN93" t="s">
-        <v>903</v>
+        <v>913</v>
       </c>
       <c r="CO93" t="s">
-        <v>904</v>
+        <v>914</v>
       </c>
       <c r="CP93" t="s">
-        <v>905</v>
+        <v>915</v>
       </c>
       <c r="CQ93" t="s">
-        <v>906</v>
+        <v>916</v>
       </c>
       <c r="CR93" t="s">
-        <v>907</v>
+        <v>619</v>
       </c>
       <c r="CS93" t="s">
-        <v>908</v>
+        <v>917</v>
       </c>
       <c r="CT93" t="s">
-        <v>909</v>
+        <v>918</v>
       </c>
       <c r="CU93" t="s">
-        <v>910</v>
+        <v>919</v>
       </c>
       <c r="CV93" t="s">
-        <v>911</v>
+        <v>920</v>
       </c>
       <c r="CW93" t="s">
-        <v>912</v>
+        <v>921</v>
       </c>
       <c r="CX93" t="s">
-        <v>913</v>
+        <v>620</v>
       </c>
       <c r="CY93" t="s">
-        <v>914</v>
+        <v>621</v>
       </c>
       <c r="CZ93" t="s">
-        <v>915</v>
+        <v>922</v>
       </c>
       <c r="DA93" t="s">
-        <v>916</v>
+        <v>923</v>
       </c>
       <c r="DB93" t="s">
-        <v>917</v>
+        <v>924</v>
       </c>
       <c r="DC93" t="s">
-        <v>918</v>
+        <v>925</v>
       </c>
       <c r="DD93" t="s">
-        <v>919</v>
+        <v>926</v>
       </c>
       <c r="DE93" t="s">
-        <v>920</v>
+        <v>927</v>
       </c>
       <c r="DF93" t="s">
-        <v>921</v>
+        <v>622</v>
       </c>
       <c r="DG93" t="s">
-        <v>922</v>
+        <v>623</v>
       </c>
       <c r="DH93" t="s">
-        <v>923</v>
+        <v>928</v>
       </c>
       <c r="DI93" t="s">
-        <v>924</v>
+        <v>929</v>
       </c>
       <c r="DJ93" t="s">
-        <v>925</v>
+        <v>930</v>
       </c>
       <c r="DK93" t="s">
-        <v>926</v>
+        <v>931</v>
       </c>
       <c r="DL93" t="s">
-        <v>927</v>
+        <v>932</v>
       </c>
       <c r="DM93" t="s">
-        <v>928</v>
+        <v>933</v>
       </c>
       <c r="DN93" t="s">
-        <v>929</v>
+        <v>934</v>
       </c>
       <c r="DO93" t="s">
-        <v>930</v>
+        <v>935</v>
       </c>
       <c r="DP93" t="s">
-        <v>931</v>
+        <v>624</v>
       </c>
       <c r="DQ93" t="s">
-        <v>932</v>
+        <v>936</v>
       </c>
       <c r="DR93" t="s">
-        <v>933</v>
+        <v>937</v>
       </c>
       <c r="DS93" t="s">
-        <v>934</v>
+        <v>938</v>
       </c>
       <c r="DT93" t="s">
-        <v>935</v>
+        <v>939</v>
       </c>
       <c r="DU93" t="s">
-        <v>936</v>
+        <v>625</v>
       </c>
       <c r="DV93" t="s">
-        <v>937</v>
+        <v>626</v>
       </c>
       <c r="DW93" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="DX93" t="s">
-        <v>939</v>
+        <v>432</v>
       </c>
       <c r="DY93" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="DZ93" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="EA93" t="s">
-        <v>942</v>
+        <v>627</v>
       </c>
       <c r="EB93" t="s">
         <v>943</v>
@@ -7747,43 +7738,43 @@
         <v>944</v>
       </c>
       <c r="ED93" t="s">
+        <v>628</v>
+      </c>
+      <c r="EE93" t="s">
         <v>945</v>
       </c>
-      <c r="EE93" t="s">
+      <c r="EF93" t="s">
+        <v>629</v>
+      </c>
+      <c r="EG93" t="s">
         <v>946</v>
       </c>
-      <c r="EF93" t="s">
+      <c r="EH93" t="s">
         <v>947</v>
       </c>
-      <c r="EG93" t="s">
+      <c r="EI93" t="s">
+        <v>630</v>
+      </c>
+      <c r="EJ93" t="s">
         <v>948</v>
       </c>
-      <c r="EH93" t="s">
+      <c r="EK93" t="s">
         <v>949</v>
       </c>
-      <c r="EI93" t="s">
+      <c r="EL93" t="s">
         <v>950</v>
       </c>
-      <c r="EJ93" t="s">
+      <c r="EM93" t="s">
         <v>951</v>
       </c>
-      <c r="EK93" t="s">
+      <c r="EN93" t="s">
         <v>952</v>
       </c>
-      <c r="EL93" t="s">
+      <c r="EO93" t="s">
         <v>953</v>
       </c>
-      <c r="EM93" t="s">
+      <c r="EP93" t="s">
         <v>954</v>
-      </c>
-      <c r="EN93" t="s">
-        <v>955</v>
-      </c>
-      <c r="EO93" t="s">
-        <v>956</v>
-      </c>
-      <c r="EP93" t="s">
-        <v>957</v>
       </c>
     </row>
   </sheetData>
@@ -7794,14 +7785,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{737D733D-CC6B-47D4-9BB9-02D7FDB4ACAA}">
   <dimension ref="A1:I70"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>30</v>
       </c>
@@ -7830,7 +7821,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -7859,7 +7850,7 @@
         <v>0.13280496999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>80</v>
       </c>
@@ -7867,7 +7858,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -7896,7 +7887,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>44</v>
       </c>
@@ -7925,7 +7916,7 @@
         <v>1.5125487999999999E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>43</v>
       </c>
@@ -7954,7 +7945,7 @@
         <v>0.13014054</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>80</v>
       </c>
@@ -7962,7 +7953,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>81</v>
       </c>
@@ -7991,7 +7982,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>299</v>
       </c>
@@ -8020,7 +8011,7 @@
         <v>3.4512825000000001E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>300</v>
       </c>
@@ -8049,7 +8040,7 @@
         <v>3.0187526999999998E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>301</v>
       </c>
@@ -8078,7 +8069,7 @@
         <v>9.7992468999999992E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>302</v>
       </c>
@@ -8107,7 +8098,7 @@
         <v>3.0890102999999999E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>303</v>
       </c>
@@ -8136,7 +8127,7 @@
         <v>8.0296702999999997E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>304</v>
       </c>
@@ -8165,7 +8156,7 @@
         <v>8.7017004000000003E-4</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>305</v>
       </c>
@@ -8194,7 +8185,7 @@
         <v>5.0508133999999996E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>306</v>
       </c>
@@ -8223,7 +8214,7 @@
         <v>8.9042532999999997E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>307</v>
       </c>
@@ -8252,7 +8243,7 @@
         <v>4.9301114999999996E-4</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>308</v>
       </c>
@@ -8281,7 +8272,7 @@
         <v>4.3122483000000001E-4</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>309</v>
       </c>
@@ -8310,7 +8301,7 @@
         <v>1.3998095000000001E-3</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>310</v>
       </c>
@@ -8339,7 +8330,7 @@
         <v>4.4126104000000001E-3</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>311</v>
       </c>
@@ -8368,7 +8359,7 @@
         <v>1.1470278E-3</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>312</v>
       </c>
@@ -8397,7 +8388,7 @@
         <v>1.2430264000000001E-4</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>313</v>
       </c>
@@ -8426,7 +8417,7 @@
         <v>7.2150201999999998E-4</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>314</v>
       </c>
@@ -8455,7 +8446,7 @@
         <v>1.2719608E-3</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>315</v>
       </c>
@@ -8484,7 +8475,7 @@
         <v>7.1858045000000003E-9</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>316</v>
       </c>
@@ -8513,7 +8504,7 @@
         <v>6.2852481000000002E-9</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>317</v>
       </c>
@@ -8542,7 +8533,7 @@
         <v>2.0402697E-8</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>318</v>
       </c>
@@ -8571,7 +8562,7 @@
         <v>6.4315291000000001E-8</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>319</v>
       </c>
@@ -8600,7 +8591,7 @@
         <v>1.6718319E-8</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>320</v>
       </c>
@@ -8629,7 +8620,7 @@
         <v>1.8117531E-9</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>321</v>
       </c>
@@ -8658,7 +8649,7 @@
         <v>1.0516136E-8</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>322</v>
       </c>
@@ -8687,7 +8678,7 @@
         <v>1.8539260000000002E-8</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>84</v>
       </c>
@@ -8716,7 +8707,7 @@
         <v>2.9138040999999999E-21</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>85</v>
       </c>
@@ -8745,7 +8736,7 @@
         <v>2.4142289E-4</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>323</v>
       </c>
@@ -8774,7 +8765,7 @@
         <v>7.8757093999999995E-4</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>324</v>
       </c>
@@ -8803,7 +8794,7 @@
         <v>1.1848325E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>86</v>
       </c>
@@ -8832,7 +8823,7 @@
         <v>1.897417E-5</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>325</v>
       </c>
@@ -8861,7 +8852,7 @@
         <v>2.0182543E-10</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>326</v>
       </c>
@@ -8890,7 +8881,7 @@
         <v>6.6099348E-10</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>327</v>
       </c>
@@ -8919,7 +8910,7 @@
         <v>6.5216456E-9</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>328</v>
       </c>
@@ -8948,7 +8939,7 @@
         <v>2.2893017000000001E-8</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>329</v>
       </c>
@@ -8977,7 +8968,7 @@
         <v>6.1430905999999998E-13</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>330</v>
       </c>
@@ -9006,7 +8997,7 @@
         <v>5.2123965000000003E-12</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>331</v>
       </c>
@@ -9035,7 +9026,7 @@
         <v>3.6968684E-3</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>332</v>
       </c>
@@ -9064,7 +9055,7 @@
         <v>4.6544734999999999E-3</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>333</v>
       </c>
@@ -9093,7 +9084,7 @@
         <v>2.3081585E-3</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>334</v>
       </c>
@@ -9122,7 +9113,7 @@
         <v>2.5055417000000003E-4</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>335</v>
       </c>
@@ -9151,7 +9142,7 @@
         <v>8.4559087999999995E-7</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>336</v>
       </c>
@@ -9180,7 +9171,7 @@
         <v>6.1942764999999998E-7</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>87</v>
       </c>
@@ -9209,7 +9200,7 @@
         <v>5.9246334000000005E-4</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>88</v>
       </c>
@@ -9238,7 +9229,7 @@
         <v>2.1722675999999999E-14</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>89</v>
       </c>
@@ -9267,7 +9258,7 @@
         <v>3.4739669999999999E-8</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>337</v>
       </c>
@@ -9296,7 +9287,7 @@
         <v>4.8900734999999997E-4</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>338</v>
       </c>
@@ -9325,7 +9316,7 @@
         <v>4.9930406999999998E-11</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>90</v>
       </c>
@@ -9354,7 +9345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>91</v>
       </c>
@@ -9383,7 +9374,7 @@
         <v>4.5211512000000002E-3</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>339</v>
       </c>
@@ -9412,7 +9403,7 @@
         <v>3.0864066999999999E-2</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>340</v>
       </c>
@@ -9441,7 +9432,7 @@
         <v>2.2609108999999999E-2</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>92</v>
       </c>
@@ -9470,7 +9461,7 @@
         <v>1.9660129000000001E-6</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>341</v>
       </c>
@@ -9499,7 +9490,7 @@
         <v>1.4299489000000001E-5</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>342</v>
       </c>
@@ -9528,7 +9519,7 @@
         <v>1.7466736000000001E-6</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>343</v>
       </c>
@@ -9557,7 +9548,7 @@
         <v>2.3030034000000001E-7</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>80</v>
       </c>
